--- a/budgetpsa-2026.xlsx
+++ b/budgetpsa-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2308A493-B589-4C77-AC4E-D0DF6EA4D3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2350F8E0-2E2F-435D-8F7C-A9863A681AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{8D383C00-7A79-4D68-BF41-98FF49B397AB}"/>
   </bookViews>
@@ -2570,7 +2570,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -2611,7 +2611,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
@@ -3022,7 +3022,7 @@
         <v>2725.3269085848133</v>
       </c>
       <c r="F2" s="1">
-        <v>1748.9959442637432</v>
+        <v>1609.0762687226438</v>
       </c>
       <c r="G2" s="1">
         <v>1985.1221279435599</v>
@@ -3034,7 +3034,7 @@
         <v>1518.3550584441759</v>
       </c>
       <c r="J2" s="1">
-        <v>2038.2803718345979</v>
+        <v>1875.2179420878301</v>
       </c>
       <c r="K2" s="1">
         <v>2199.5310459908378</v>
@@ -3049,7 +3049,8 @@
         <v>2113.9496625421825</v>
       </c>
       <c r="O2" s="1">
-        <v>21760.687600265479</v>
+        <f>+SUM(C2:N2)</f>
+        <v>22039.105902757208</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -3069,7 +3070,7 @@
         <v>1004.4890661597476</v>
       </c>
       <c r="F3" s="1">
-        <v>1658.6863430108822</v>
+        <v>1525.9914355700116</v>
       </c>
       <c r="G3" s="1">
         <v>1085.1189055200689</v>
@@ -3081,7 +3082,7 @@
         <v>1118.6165417170496</v>
       </c>
       <c r="J3" s="1">
-        <v>1205.1646543434126</v>
+        <v>1108.7514819959397</v>
       </c>
       <c r="K3" s="1">
         <v>1021.9060169426458</v>
@@ -3096,7 +3097,8 @@
         <v>1034.6609181664794</v>
       </c>
       <c r="O3" s="1">
-        <v>14660.400407698873</v>
+        <f t="shared" ref="O3:O66" si="0">+SUM(C3:N3)</f>
+        <v>15115.60608211669</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -3116,7 +3118,7 @@
         <v>1297.9652873485184</v>
       </c>
       <c r="F4" s="1">
-        <v>1402.809139461109</v>
+        <v>1290.5844083042205</v>
       </c>
       <c r="G4" s="1">
         <v>1195.9447421107827</v>
@@ -3128,7 +3130,7 @@
         <v>722.94868198307142</v>
       </c>
       <c r="J4" s="1">
-        <v>1137.8306442996047</v>
+        <v>1046.8041927556364</v>
       </c>
       <c r="K4" s="1">
         <v>816.443431525606</v>
@@ -3143,7 +3145,8 @@
         <v>970.06801181102367</v>
       </c>
       <c r="O4" s="1">
-        <v>12097.724924623117</v>
+        <f t="shared" si="0"/>
+        <v>12582.071823473356</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -3163,7 +3166,7 @@
         <v>1143.2232798126211</v>
       </c>
       <c r="F5" s="1">
-        <v>857.9412119021805</v>
+        <v>789.30591495000601</v>
       </c>
       <c r="G5" s="1">
         <v>600.40810372771477</v>
@@ -3175,7 +3178,7 @@
         <v>827.97163240628788</v>
       </c>
       <c r="J5" s="1">
-        <v>1885.3522812266269</v>
+        <v>1734.5240987284969</v>
       </c>
       <c r="K5" s="1">
         <v>1016.4991068000921</v>
@@ -3190,7 +3193,8 @@
         <v>749.27771372328471</v>
       </c>
       <c r="O5" s="1">
-        <v>11632.385400587846</v>
+        <f t="shared" si="0"/>
+        <v>11775.537215224564</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -3222,7 +3226,7 @@
         <v>1434.4995243853286</v>
       </c>
       <c r="J6" s="1">
-        <v>166.623143498237</v>
+        <v>153.29329201837803</v>
       </c>
       <c r="K6" s="1">
         <v>3008.4048033168688</v>
@@ -3237,7 +3241,8 @@
         <v>1934.2639412260969</v>
       </c>
       <c r="O6" s="1">
-        <v>11317.013116526028</v>
+        <f t="shared" si="0"/>
+        <v>10636.529137362904</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -3257,7 +3262,7 @@
         <v>753.70029532570697</v>
       </c>
       <c r="F7" s="1">
-        <v>1175.5299763080754</v>
+        <v>1081.4875782034294</v>
       </c>
       <c r="G7" s="1">
         <v>473.75000476689871</v>
@@ -3269,7 +3274,7 @@
         <v>702.59539701733172</v>
       </c>
       <c r="J7" s="1">
-        <v>505.57570253232183</v>
+        <v>465.12964632973609</v>
       </c>
       <c r="K7" s="1">
         <v>606.6553179945231</v>
@@ -3284,7 +3289,8 @@
         <v>521.440916760405</v>
       </c>
       <c r="O7" s="1">
-        <v>8038.685142694605</v>
+        <f t="shared" si="0"/>
+        <v>8198.8210153221025</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
@@ -3304,7 +3310,7 @@
         <v>2571.9188838725013</v>
       </c>
       <c r="F8" s="1">
-        <v>490.68216680721201</v>
+        <v>451.42759346263506</v>
       </c>
       <c r="G8" s="1">
         <v>717.32327199923725</v>
@@ -3331,7 +3337,8 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>7222.6869251919979</v>
+        <f t="shared" si="0"/>
+        <v>7139.7548963900672</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
@@ -3351,7 +3358,7 @@
         <v>783.04791744458396</v>
       </c>
       <c r="F9" s="1">
-        <v>1118.3338955145966</v>
+        <v>1028.867183873429</v>
       </c>
       <c r="G9" s="1">
         <v>479.83933644770713</v>
@@ -3363,7 +3370,7 @@
         <v>256.45139056831925</v>
       </c>
       <c r="J9" s="1">
-        <v>870.77711293941661</v>
+        <v>801.11494390426333</v>
       </c>
       <c r="K9" s="1">
         <v>456.34321603153074</v>
@@ -3378,7 +3385,8 @@
         <v>815.0450365579303</v>
       </c>
       <c r="O9" s="1">
-        <v>7875.4854991940838</v>
+        <f t="shared" si="0"/>
+        <v>8065.5890518580591</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -3398,7 +3406,7 @@
         <v>600.29227061339498</v>
       </c>
       <c r="F10" s="1">
-        <v>1407.3246195237523</v>
+        <v>1294.7386499618522</v>
       </c>
       <c r="G10" s="1">
         <v>462.78920774144348</v>
@@ -3410,7 +3418,7 @@
         <v>298.78622329705763</v>
       </c>
       <c r="J10" s="1">
-        <v>809.14937493321941</v>
+        <v>744.41742493856179</v>
       </c>
       <c r="K10" s="1">
         <v>235.74128221534053</v>
@@ -3425,7 +3433,8 @@
         <v>715.21963582677176</v>
       </c>
       <c r="O10" s="1">
-        <v>7357.2163610505368</v>
+        <f t="shared" si="0"/>
+        <v>7624.1860991616868</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
@@ -3445,7 +3454,7 @@
         <v>360.17536236803699</v>
       </c>
       <c r="F11" s="1">
-        <v>764.62129060755728</v>
+        <v>703.45158735895279</v>
       </c>
       <c r="G11" s="1">
         <v>501.7609304986176</v>
@@ -3457,7 +3466,7 @@
         <v>304.48514308746479</v>
       </c>
       <c r="J11" s="1">
-        <v>795.45432204295321</v>
+        <v>731.81797627951698</v>
       </c>
       <c r="K11" s="1">
         <v>475.80809254472399</v>
@@ -3472,7 +3481,8 @@
         <v>711.69638638920139</v>
       </c>
       <c r="O11" s="1">
-        <v>7104.6979937422975</v>
+        <f t="shared" si="0"/>
+        <v>7305.3903692268777</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -3492,7 +3502,7 @@
         <v>352.171465426525</v>
       </c>
       <c r="F12" s="1">
-        <v>739.03357025258003</v>
+        <v>679.91088463237361</v>
       </c>
       <c r="G12" s="1">
         <v>161.97622270950521</v>
@@ -3504,7 +3514,7 @@
         <v>638.27901652559456</v>
       </c>
       <c r="J12" s="1">
-        <v>528.40079068276521</v>
+        <v>486.12872742814403</v>
       </c>
       <c r="K12" s="1">
         <v>350.36777723747861</v>
@@ -3519,7 +3529,8 @@
         <v>1350.5789510686166</v>
       </c>
       <c r="O12" s="1">
-        <v>7614.1455295344658</v>
+        <f t="shared" si="0"/>
+        <v>7476.6474116982581</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -3539,7 +3550,7 @@
         <v>149.40607624155606</v>
       </c>
       <c r="F13" s="1">
-        <v>404.88804561699391</v>
+        <v>372.49700196763439</v>
       </c>
       <c r="G13" s="1">
         <v>362.92416817618459</v>
@@ -3551,7 +3562,7 @@
         <v>474.63860540104798</v>
       </c>
       <c r="J13" s="1">
-        <v>1248.5323218292551</v>
+        <v>1148.6497360829148</v>
       </c>
       <c r="K13" s="1">
         <v>790.49026284134823</v>
@@ -3566,7 +3577,8 @@
         <v>546.10366282339714</v>
       </c>
       <c r="O13" s="1">
-        <v>6526.8830397269376</v>
+        <f t="shared" si="0"/>
+        <v>6544.2499928009775</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
@@ -3586,7 +3598,7 @@
         <v>316.15392918972128</v>
       </c>
       <c r="F14" s="1">
-        <v>615.61044854033651</v>
+        <v>566.3616126571095</v>
       </c>
       <c r="G14" s="1">
         <v>448.17481170750312</v>
@@ -3598,7 +3610,7 @@
         <v>411.13635630794039</v>
       </c>
       <c r="J14" s="1">
-        <v>990.6088257292447</v>
+        <v>911.36011967090508</v>
       </c>
       <c r="K14" s="1">
         <v>394.70444040641877</v>
@@ -3613,7 +3625,8 @@
         <v>162.06947412823399</v>
       </c>
       <c r="O14" s="1">
-        <v>6047.2084118706753</v>
+        <f t="shared" si="0"/>
+        <v>6173.9035874294595</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -3633,7 +3646,7 @@
         <v>514.91736990393429</v>
       </c>
       <c r="F15" s="1">
-        <v>224.26884311127174</v>
+        <v>206.32733566236999</v>
       </c>
       <c r="G15" s="1">
         <v>779.43445514348366</v>
@@ -3645,7 +3658,7 @@
         <v>196.20566706972994</v>
       </c>
       <c r="J15" s="1">
-        <v>356.07137514691738</v>
+        <v>327.58566513516399</v>
       </c>
       <c r="K15" s="1">
         <v>288.72900161236663</v>
@@ -3660,7 +3673,8 @@
         <v>620.09190101237346</v>
       </c>
       <c r="O15" s="1">
-        <v>5797.9981454442031</v>
+        <f t="shared" si="0"/>
+        <v>5824.9742843427539</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
@@ -3680,7 +3694,7 @@
         <v>692.33708544078218</v>
       </c>
       <c r="F16" s="1">
-        <v>1547.3045014656871</v>
+        <v>1423.5201413484319</v>
       </c>
       <c r="G16" s="1">
         <v>284.98072266183624</v>
@@ -3692,7 +3706,7 @@
         <v>328.09495364772272</v>
       </c>
       <c r="J16" s="1">
-        <v>246.51095202478896</v>
+        <v>226.79007586280585</v>
       </c>
       <c r="K16" s="1">
         <v>366.58850766513967</v>
@@ -3707,7 +3721,8 @@
         <v>380.51093925759284</v>
       </c>
       <c r="O16" s="1">
-        <v>4658.9087418223189</v>
+        <f t="shared" si="0"/>
+        <v>4996.8552811996642</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
@@ -3727,7 +3742,7 @@
         <v>553.60287178790861</v>
       </c>
       <c r="F17" s="1">
-        <v>407.89836565875601</v>
+        <v>375.26649640605552</v>
       </c>
       <c r="G17" s="1">
         <v>243.57326723233865</v>
@@ -3754,7 +3769,8 @@
         <v>156.19739173228348</v>
       </c>
       <c r="O17" s="1">
-        <v>4411.9038759836922</v>
+        <f t="shared" si="0"/>
+        <v>4458.61565253756</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
@@ -3786,7 +3802,7 @@
         <v>1682.809600967352</v>
       </c>
       <c r="J18" s="1">
-        <v>551.22587883320864</v>
+        <v>507.12780852655203</v>
       </c>
       <c r="K18" s="1">
         <v>857.53594860901387</v>
@@ -3801,7 +3817,8 @@
         <v>0</v>
       </c>
       <c r="O18" s="1">
-        <v>4206.8016213141182</v>
+        <f t="shared" si="0"/>
+        <v>3684.0282350821299</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
@@ -3821,7 +3838,7 @@
         <v>142.73616212362947</v>
       </c>
       <c r="F19" s="1">
-        <v>576.47628799743006</v>
+        <v>530.35818495763567</v>
       </c>
       <c r="G19" s="1">
         <v>319.08098007436365</v>
@@ -3848,7 +3865,8 @@
         <v>489.73167182227223</v>
       </c>
       <c r="O19" s="1">
-        <v>4461.5253892102019</v>
+        <f t="shared" si="0"/>
+        <v>4565.7787808334624</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -3868,7 +3886,7 @@
         <v>218.77318306799282</v>
       </c>
       <c r="F20" s="1">
-        <v>197.17596273541341</v>
+        <v>181.40188571658035</v>
       </c>
       <c r="G20" s="1">
         <v>372.66709886547812</v>
@@ -3880,7 +3898,7 @@
         <v>497.4342845626764</v>
       </c>
       <c r="J20" s="1">
-        <v>11.412544075221712</v>
+        <v>10.499540549203974</v>
       </c>
       <c r="K20" s="1">
         <v>554.74898062600778</v>
@@ -3895,7 +3913,8 @@
         <v>689.38247328458942</v>
       </c>
       <c r="O20" s="1">
-        <v>4604.8764274201203</v>
+        <f t="shared" si="0"/>
+        <v>4569.1797866477782</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -3942,7 +3961,8 @@
         <v>1167.3699803149607</v>
       </c>
       <c r="O21" s="1">
-        <v>4909.2217085427137</v>
+        <f t="shared" si="0"/>
+        <v>4593.2779466913853</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -3962,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>555.40404770509576</v>
+        <v>510.97172388868813</v>
       </c>
       <c r="G22" s="1">
         <v>48.714653446467729</v>
@@ -3974,7 +3994,7 @@
         <v>172.59585650947201</v>
       </c>
       <c r="J22" s="1">
-        <v>118.69045838230579</v>
+        <v>109.19522171172133</v>
       </c>
       <c r="K22" s="1">
         <v>315.76355232513504</v>
@@ -3989,7 +4009,8 @@
         <v>540.2315804274466</v>
       </c>
       <c r="O22" s="1">
-        <v>4311.5581492367501</v>
+        <f t="shared" si="0"/>
+        <v>4261.5602903601402</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -4009,7 +4030,7 @@
         <v>385.52103601615806</v>
       </c>
       <c r="F23" s="1">
-        <v>425.96028590932821</v>
+        <v>391.88346303658199</v>
       </c>
       <c r="G23" s="1">
         <v>297.15938602345318</v>
@@ -4021,7 +4042,7 @@
         <v>295.52969770253935</v>
       </c>
       <c r="J23" s="1">
-        <v>84.452826156640654</v>
+        <v>77.696600064109404</v>
       </c>
       <c r="K23" s="1">
         <v>363.34436157960738</v>
@@ -4036,7 +4057,8 @@
         <v>327.66219769403824</v>
       </c>
       <c r="O23" s="1">
-        <v>4098.7369925097191</v>
+        <f t="shared" si="0"/>
+        <v>4261.2609558627191</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
@@ -4056,7 +4078,7 @@
         <v>437.54636613598564</v>
       </c>
       <c r="F24" s="1">
-        <v>394.35192547082681</v>
+        <v>362.8037714331607</v>
       </c>
       <c r="G24" s="1">
         <v>196.07648012203262</v>
@@ -4068,7 +4090,7 @@
         <v>294.71556630390978</v>
       </c>
       <c r="J24" s="1">
-        <v>86.735334971685006</v>
+        <v>79.796508173950201</v>
       </c>
       <c r="K24" s="1">
         <v>274.67103524172705</v>
@@ -4083,7 +4105,8 @@
         <v>581.33615719910017</v>
       </c>
       <c r="O24" s="1">
-        <v>4291.7095439461464</v>
+        <f t="shared" si="0"/>
+        <v>4386.5452689426629</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -4103,7 +4126,7 @@
         <v>466.89398825486273</v>
       </c>
       <c r="F25" s="1">
-        <v>147.50568204633979</v>
+        <v>135.70522748263261</v>
       </c>
       <c r="G25" s="1">
         <v>507.85026217942612</v>
@@ -4115,7 +4138,7 @@
         <v>288.20251511487305</v>
       </c>
       <c r="J25" s="1">
-        <v>42.226413078320327</v>
+        <v>38.848300032054702</v>
       </c>
       <c r="K25" s="1">
         <v>477.97085660174548</v>
@@ -4130,7 +4153,8 @@
         <v>642.40581411698543</v>
       </c>
       <c r="O25" s="1">
-        <v>4242.0880307196367</v>
+        <f t="shared" si="0"/>
+        <v>4239.4957645557351</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -4150,7 +4174,7 @@
         <v>472.229919549204</v>
       </c>
       <c r="F26" s="1">
-        <v>809.77609123398781</v>
+        <v>744.99400393526878</v>
       </c>
       <c r="G26" s="1">
         <v>202.16581180284109</v>
@@ -4162,7 +4186,7 @@
         <v>66.758774687625959</v>
       </c>
       <c r="J26" s="1">
-        <v>222.54460946682337</v>
+        <v>204.74104070947752</v>
       </c>
       <c r="K26" s="1">
         <v>530.95857599877161</v>
@@ -4177,7 +4201,8 @@
         <v>214.91821569178853</v>
       </c>
       <c r="O26" s="1">
-        <v>3709.4837887550966</v>
+        <f t="shared" si="0"/>
+        <v>4001.0189198595099</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -4197,7 +4222,7 @@
         <v>272.13249601140569</v>
       </c>
       <c r="F27" s="1">
-        <v>135.46440187929164</v>
+        <v>124.62724972894831</v>
       </c>
       <c r="G27" s="1">
         <v>142.49036133091812</v>
@@ -4209,7 +4234,7 @@
         <v>699.33887142281344</v>
       </c>
       <c r="J27" s="1">
-        <v>164.34063468319266</v>
+        <v>151.19338390853724</v>
       </c>
       <c r="K27" s="1">
         <v>501.76126122898171</v>
@@ -4224,7 +4249,8 @@
         <v>223.13913104611925</v>
       </c>
       <c r="O27" s="1">
-        <v>3683.0189817009582</v>
+        <f t="shared" si="0"/>
+        <v>3476.9737288494189</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
@@ -4244,7 +4270,7 @@
         <v>316.15392918972128</v>
       </c>
       <c r="F28" s="1">
-        <v>397.36224551258886</v>
+        <v>365.57326587158173</v>
       </c>
       <c r="G28" s="1">
         <v>416.51028696729907</v>
@@ -4256,7 +4282,7 @@
         <v>416.02114469971792</v>
       </c>
       <c r="J28" s="1">
-        <v>252.21722406239982</v>
+        <v>232.03984613740784</v>
       </c>
       <c r="K28" s="1">
         <v>387.13476620684366</v>
@@ -4271,7 +4297,8 @@
         <v>209.04613329583802</v>
       </c>
       <c r="O28" s="1">
-        <v>3638.9109699440605</v>
+        <f t="shared" si="0"/>
+        <v>3685.435179834582</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
@@ -4291,7 +4318,7 @@
         <v>226.77708000950477</v>
       </c>
       <c r="F29" s="1">
-        <v>880.51861221539571</v>
+        <v>810.07712323816406</v>
       </c>
       <c r="G29" s="1">
         <v>68.200514825054825</v>
@@ -4303,7 +4330,7 @@
         <v>56.989197904070949</v>
       </c>
       <c r="J29" s="1">
-        <v>60.486483598675072</v>
+        <v>55.647564910781064</v>
       </c>
       <c r="K29" s="1">
         <v>307.11249609704913</v>
@@ -4318,7 +4345,8 @@
         <v>668.24297665916765</v>
       </c>
       <c r="O29" s="1">
-        <v>4040.2938769318293</v>
+        <f t="shared" si="0"/>
+        <v>4352.488830876182</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -4338,7 +4366,7 @@
         <v>581.61651108320041</v>
       </c>
       <c r="F30" s="1">
-        <v>364.24872505320644</v>
+        <v>335.10882704894993</v>
       </c>
       <c r="G30" s="1">
         <v>208.25514348364953</v>
@@ -4350,7 +4378,7 @@
         <v>324.83842805320438</v>
       </c>
       <c r="J30" s="1">
-        <v>118.69045838230579</v>
+        <v>109.19522171172133</v>
       </c>
       <c r="K30" s="1">
         <v>404.43687866301542</v>
@@ -4365,7 +4393,8 @@
         <v>447.45267857142858</v>
       </c>
       <c r="O30" s="1">
-        <v>3559.5165487816444</v>
+        <f t="shared" si="0"/>
+        <v>3635.7795837788699</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
@@ -4412,7 +4441,8 @@
         <v>1423.3927727784028</v>
       </c>
       <c r="O31" s="1">
-        <v>4444.9848848013662</v>
+        <f t="shared" si="0"/>
+        <v>4073.8323960932212</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -4432,7 +4462,7 @@
         <v>161.41192165382398</v>
       </c>
       <c r="F32" s="1">
-        <v>624.64140866562263</v>
+        <v>574.67009597237279</v>
       </c>
       <c r="G32" s="1">
         <v>331.25964343598054</v>
@@ -4444,7 +4474,7 @@
         <v>157.12735993550987</v>
       </c>
       <c r="J32" s="1">
-        <v>140.37429212522704</v>
+        <v>129.14434875520888</v>
       </c>
       <c r="K32" s="1">
         <v>441.20386763238042</v>
@@ -4459,7 +4489,8 @@
         <v>631.83606580427443</v>
       </c>
       <c r="O32" s="1">
-        <v>3642.2190708258272</v>
+        <f t="shared" si="0"/>
+        <v>3786.6857861073031</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
@@ -4479,7 +4510,7 @@
         <v>302.81410095386809</v>
       </c>
       <c r="F33" s="1">
-        <v>576.47628799743006</v>
+        <v>530.35818495763567</v>
       </c>
       <c r="G33" s="1">
         <v>481.05720278386883</v>
@@ -4506,7 +4537,8 @@
         <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>3037.9393097563288</v>
+        <f t="shared" si="0"/>
+        <v>3529.0015020314813</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
@@ -4526,7 +4558,7 @@
         <v>129.39633388777622</v>
       </c>
       <c r="F34" s="1">
-        <v>609.58980845681242</v>
+        <v>560.82262378026746</v>
       </c>
       <c r="G34" s="1">
         <v>79.16131185051006</v>
@@ -4538,7 +4570,7 @@
         <v>262.15031035872636</v>
       </c>
       <c r="J34" s="1">
-        <v>308.1386900309862</v>
+        <v>283.48759482850733</v>
       </c>
       <c r="K34" s="1">
         <v>169.77697847618563</v>
@@ -4553,7 +4585,8 @@
         <v>475.63867407199103</v>
       </c>
       <c r="O34" s="1">
-        <v>3483.4302285009958</v>
+        <f t="shared" si="0"/>
+        <v>3588.8200441165263</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
@@ -4573,7 +4606,7 @@
         <v>512.24940425676368</v>
       </c>
       <c r="F35" s="1">
-        <v>343.1764847608722</v>
+        <v>315.72236598000245</v>
       </c>
       <c r="G35" s="1">
         <v>369.01349985699306</v>
@@ -4585,7 +4618,7 @@
         <v>78.156614268440151</v>
       </c>
       <c r="J35" s="1">
-        <v>431.39416604338072</v>
+        <v>396.88263275991028</v>
       </c>
       <c r="K35" s="1">
         <v>734.25839735879003</v>
@@ -4600,7 +4633,8 @@
         <v>361.72027559055118</v>
       </c>
       <c r="O35" s="1">
-        <v>3352.2088935242255</v>
+        <f t="shared" si="0"/>
+        <v>3374.064383362288</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
@@ -4620,7 +4654,7 @@
         <v>212.10326895006619</v>
       </c>
       <c r="F36" s="1">
-        <v>218.24820302774765</v>
+        <v>200.78834678552784</v>
       </c>
       <c r="G36" s="1">
         <v>550.47558394508542</v>
@@ -4632,7 +4666,7 @@
         <v>289.83077791213225</v>
       </c>
       <c r="J36" s="1">
-        <v>74.181536488941134</v>
+        <v>68.247013569825839</v>
       </c>
       <c r="K36" s="1">
         <v>361.18159752258595</v>
@@ -4647,7 +4681,8 @@
         <v>248.9762935883015</v>
       </c>
       <c r="O36" s="1">
-        <v>3241.9388641319811</v>
+        <f t="shared" si="0"/>
+        <v>3332.7110505142905</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
@@ -4694,7 +4729,8 @@
         <v>735.18471597300345</v>
       </c>
       <c r="O37" s="1">
-        <v>3685.2243822888031</v>
+        <f t="shared" si="0"/>
+        <v>3366.5773797661859</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
@@ -4726,7 +4762,7 @@
         <v>1626.6345344619106</v>
       </c>
       <c r="J38" s="1">
-        <v>84.452826156640654</v>
+        <v>77.696600064109404</v>
       </c>
       <c r="K38" s="1">
         <v>41.092517083407984</v>
@@ -4741,7 +4777,8 @@
         <v>43.453409730033748</v>
       </c>
       <c r="O38" s="1">
-        <v>3007.0637015265006</v>
+        <f t="shared" si="0"/>
+        <v>2477.4620099980903</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
@@ -4761,7 +4798,7 @@
         <v>97.380746121728507</v>
       </c>
       <c r="F39" s="1">
-        <v>63.216720877002771</v>
+        <v>58.159383206842548</v>
       </c>
       <c r="G39" s="1">
         <v>708.79820764610554</v>
@@ -4773,7 +4810,7 @@
         <v>155.4990971382507</v>
       </c>
       <c r="J39" s="1">
-        <v>167.76439790575915</v>
+        <v>154.34324607329842</v>
       </c>
       <c r="K39" s="1">
         <v>653.15474522048476</v>
@@ -4788,7 +4825,8 @@
         <v>157.37180821147359</v>
       </c>
       <c r="O39" s="1">
-        <v>3112.9229297430552</v>
+        <f t="shared" si="0"/>
+        <v>3279.8725693418482</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
@@ -4808,7 +4846,7 @@
         <v>268.13054754064973</v>
       </c>
       <c r="F40" s="1">
-        <v>243.83592338272496</v>
+        <v>224.32904951210696</v>
       </c>
       <c r="G40" s="1">
         <v>12.178663361616932</v>
@@ -4820,7 +4858,7 @@
         <v>175.03825070536078</v>
       </c>
       <c r="J40" s="1">
-        <v>47.932685115931186</v>
+        <v>44.098070306656695</v>
       </c>
       <c r="K40" s="1">
         <v>462.83150820259522</v>
@@ -4835,7 +4873,8 @@
         <v>126.83697975253094</v>
       </c>
       <c r="O40" s="1">
-        <v>2910.0260756613256</v>
+        <f t="shared" si="0"/>
+        <v>2988.9793111145414</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
@@ -4855,7 +4894,7 @@
         <v>514.91736990393429</v>
       </c>
       <c r="F41" s="1">
-        <v>176.10372244307914</v>
+        <v>162.01542464763281</v>
       </c>
       <c r="G41" s="1">
         <v>91.339975212127001</v>
@@ -4867,7 +4906,7 @@
         <v>17.910890769850866</v>
       </c>
       <c r="J41" s="1">
-        <v>19.40132492787691</v>
+        <v>17.849218933646757</v>
       </c>
       <c r="K41" s="1">
         <v>639.09677884984524</v>
@@ -4882,7 +4921,8 @@
         <v>332.3598636107987</v>
       </c>
       <c r="O41" s="1">
-        <v>2996.0366985872761</v>
+        <f t="shared" si="0"/>
+        <v>2950.9412407251839</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
@@ -4914,7 +4954,7 @@
         <v>576.4050302297461</v>
       </c>
       <c r="J42" s="1">
-        <v>68.475264451330276</v>
+        <v>62.997243295223853</v>
       </c>
       <c r="K42" s="1">
         <v>45.418045197450923</v>
@@ -4929,7 +4969,8 @@
         <v>885.51002530933636</v>
       </c>
       <c r="O42" s="1">
-        <v>3452.5546202711676</v>
+        <f t="shared" si="0"/>
+        <v>3340.4762512572861</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
@@ -4949,7 +4990,7 @@
         <v>915.1122169795309</v>
       </c>
       <c r="F43" s="1">
-        <v>498.20796691161706</v>
+        <v>458.35132955868772</v>
       </c>
       <c r="G43" s="1">
         <v>131.52956430546288</v>
@@ -4976,7 +5017,8 @@
         <v>179.68572131608551</v>
       </c>
       <c r="O43" s="1">
-        <v>2764.4696368635637</v>
+        <f t="shared" si="0"/>
+        <v>2941.7741094309768</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
@@ -4996,7 +5038,7 @@
         <v>156.07599035948269</v>
       </c>
       <c r="F44" s="1">
-        <v>82.783801148456007</v>
+        <v>76.161097056579536</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
@@ -5008,7 +5050,7 @@
         <v>227.1426602176542</v>
       </c>
       <c r="J44" s="1">
-        <v>68.475264451330276</v>
+        <v>62.997243295223853</v>
       </c>
       <c r="K44" s="1">
         <v>501.76126122898171</v>
@@ -5023,7 +5065,8 @@
         <v>589.55707255343077</v>
       </c>
       <c r="O44" s="1">
-        <v>3087.560822982839</v>
+        <f t="shared" si="0"/>
+        <v>2987.6939608243097</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
@@ -5043,7 +5086,7 @@
         <v>733.6905529719271</v>
       </c>
       <c r="F45" s="1">
-        <v>146.00052202545879</v>
+        <v>134.32048026342207</v>
       </c>
       <c r="G45" s="1">
         <v>30.446658404042331</v>
@@ -5055,7 +5098,7 @@
         <v>155.4990971382507</v>
       </c>
       <c r="J45" s="1">
-        <v>195.15450368629126</v>
+        <v>179.54214339138798</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -5070,7 +5113,8 @@
         <v>617.74306805399328</v>
       </c>
       <c r="O45" s="1">
-        <v>3087.560822982839</v>
+        <f t="shared" si="0"/>
+        <v>3131.2983211012629</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
@@ -5090,7 +5134,7 @@
         <v>586.95244237754173</v>
       </c>
       <c r="F46" s="1">
-        <v>296.51652411356065</v>
+        <v>272.79520218447578</v>
       </c>
       <c r="G46" s="1">
         <v>170.50128706263706</v>
@@ -5102,7 +5146,7 @@
         <v>188.87848448206373</v>
       </c>
       <c r="J46" s="1">
-        <v>90.159098194251527</v>
+        <v>82.946370338711404</v>
       </c>
       <c r="K46" s="1">
         <v>419.57622706216574</v>
@@ -5117,7 +5161,8 @@
         <v>199.65080146231725</v>
       </c>
       <c r="O46" s="1">
-        <v>2677.3563136436906</v>
+        <f t="shared" si="0"/>
+        <v>2827.8997193832411</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
@@ -5164,7 +5209,8 @@
         <v>266.59254077615299</v>
       </c>
       <c r="O47" s="1">
-        <v>2650.8915065895517</v>
+        <f t="shared" si="0"/>
+        <v>2824.3603608532035</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
@@ -5184,7 +5230,7 @@
         <v>45.355416001900949</v>
       </c>
       <c r="F48" s="1">
-        <v>287.48556398827452</v>
+        <v>264.48671886921255</v>
       </c>
       <c r="G48" s="1">
         <v>187.55141576890077</v>
@@ -5196,7 +5242,7 @@
         <v>949.27721080209596</v>
       </c>
       <c r="J48" s="1">
-        <v>219.12084624425688</v>
+        <v>201.59117854471634</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -5211,7 +5257,8 @@
         <v>28.185995500562431</v>
       </c>
       <c r="O48" s="1">
-        <v>2357.5732284061824</v>
+        <f t="shared" si="0"/>
+        <v>2061.2721164873778</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
@@ -5231,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>466.59960647311567</v>
+        <v>429.27163795526644</v>
       </c>
       <c r="G49" s="1">
         <v>196.07648012203262</v>
@@ -5258,7 +5305,8 @@
         <v>38.755743813273341</v>
       </c>
       <c r="O49" s="1">
-        <v>2298.0274125343699</v>
+        <f t="shared" si="0"/>
+        <v>2260.967397392732</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
@@ -5305,7 +5353,8 @@
         <v>709.34755343082111</v>
       </c>
       <c r="O50" s="1">
-        <v>2830.6316544989099</v>
+        <f t="shared" si="0"/>
+        <v>2604.8118631348316</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
@@ -5325,7 +5374,7 @@
         <v>1624.7910791269221</v>
       </c>
       <c r="F51" s="1">
-        <v>576.47628799743006</v>
+        <v>530.35818495763567</v>
       </c>
       <c r="G51" s="1">
         <v>136.40102965010965</v>
@@ -5352,7 +5401,8 @@
         <v>0</v>
       </c>
       <c r="O51" s="1">
-        <v>2119.3899649189343</v>
+        <f t="shared" si="0"/>
+        <v>2603.217028411339</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
@@ -5372,7 +5422,7 @@
         <v>158.74395600665332</v>
       </c>
       <c r="F52" s="1">
-        <v>25.587720354977311</v>
+        <v>23.540702726579127</v>
       </c>
       <c r="G52" s="1">
         <v>124.22236628849272</v>
@@ -5399,7 +5449,8 @@
         <v>1431.6136881327336</v>
       </c>
       <c r="O52" s="1">
-        <v>3430.5006143927185</v>
+        <f t="shared" si="0"/>
+        <v>3430.4395935369848</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
@@ -5446,7 +5497,8 @@
         <v>0</v>
       </c>
       <c r="O53" s="1">
-        <v>2064.2549502228121</v>
+        <f t="shared" si="0"/>
+        <v>1696.6683747508755</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
@@ -5466,7 +5518,7 @@
         <v>573.61261414168848</v>
       </c>
       <c r="F54" s="1">
-        <v>30.103200417620368</v>
+        <v>27.694944384210736</v>
       </c>
       <c r="G54" s="1">
         <v>17.050128706263706</v>
@@ -5478,7 +5530,7 @@
         <v>385.08415155179364</v>
       </c>
       <c r="J54" s="1">
-        <v>212.27331979912384</v>
+        <v>195.29145421519394</v>
       </c>
       <c r="K54" s="1">
         <v>255.20615872853378</v>
@@ -5493,7 +5545,8 @@
         <v>37.581327334083248</v>
       </c>
       <c r="O54" s="1">
-        <v>2089.6170569830283</v>
+        <f t="shared" si="0"/>
+        <v>2073.1060009659955</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
@@ -5513,7 +5566,7 @@
         <v>41.353467531144986</v>
       </c>
       <c r="F55" s="1">
-        <v>97.835401357266193</v>
+        <v>90.008569248684893</v>
       </c>
       <c r="G55" s="1">
         <v>69.418381161216516</v>
@@ -5525,7 +5578,7 @@
         <v>860.53688835147125</v>
       </c>
       <c r="J55" s="1">
-        <v>30.81386900309862</v>
+        <v>28.348759482850731</v>
       </c>
       <c r="K55" s="1">
         <v>316.84493435364578</v>
@@ -5540,7 +5593,8 @@
         <v>83.383570022497196</v>
       </c>
       <c r="O55" s="1">
-        <v>2109.4656622736325</v>
+        <f t="shared" si="0"/>
+        <v>1882.3468432509685</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
@@ -5587,7 +5641,8 @@
         <v>229.01121344206976</v>
       </c>
       <c r="O56" s="1">
-        <v>2212.0167896084195</v>
+        <f t="shared" si="0"/>
+        <v>2007.5688083138625</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
@@ -5607,7 +5662,7 @@
         <v>270.79851318782039</v>
       </c>
       <c r="F57" s="1">
-        <v>319.09392442677586</v>
+        <v>293.56641047263383</v>
       </c>
       <c r="G57" s="1">
         <v>69.418381161216516</v>
@@ -5619,7 +5674,7 @@
         <v>132.70341797662235</v>
       </c>
       <c r="J57" s="1">
-        <v>228.25088150443426</v>
+        <v>209.99081098407953</v>
       </c>
       <c r="K57" s="1">
         <v>155.71901210554603</v>
@@ -5634,7 +5689,8 @@
         <v>151.49972581552308</v>
       </c>
       <c r="O57" s="1">
-        <v>2086.3089561012612</v>
+        <f t="shared" si="0"/>
+        <v>2191.2287662387066</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
@@ -5681,7 +5737,8 @@
         <v>125.66256327334084</v>
       </c>
       <c r="O58" s="1">
-        <v>2055.4333478714329</v>
+        <f t="shared" si="0"/>
+        <v>1783.7832200201544</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
@@ -5713,7 +5770,7 @@
         <v>135.14581217251109</v>
       </c>
       <c r="J59" s="1">
-        <v>200.86077572390212</v>
+        <v>184.79191366598997</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -5728,7 +5785,8 @@
         <v>292.42970331833521</v>
       </c>
       <c r="O59" s="1">
-        <v>2195.4762851995829</v>
+        <f t="shared" si="0"/>
+        <v>2331.0646023326972</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
@@ -5748,7 +5806,7 @@
         <v>230.77902848026071</v>
       </c>
       <c r="F60" s="1">
-        <v>48.165120668192586</v>
+        <v>44.311911014737177</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
@@ -5760,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>520.41200983011004</v>
+        <v>478.77904904370126</v>
       </c>
       <c r="K60" s="1">
         <v>49.743573311493883</v>
@@ -5775,7 +5833,8 @@
         <v>0</v>
       </c>
       <c r="O60" s="1">
-        <v>1867.9742979046177</v>
+        <f t="shared" si="0"/>
+        <v>1862.0623879967893</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
@@ -5795,7 +5854,7 @@
         <v>74.703038120778032</v>
       </c>
       <c r="F61" s="1">
-        <v>188.14500261012731</v>
+        <v>173.09340240131712</v>
       </c>
       <c r="G61" s="1">
         <v>35.318123748689104</v>
@@ -5807,7 +5866,7 @@
         <v>221.44374042724709</v>
       </c>
       <c r="J61" s="1">
-        <v>63.910246821241586</v>
+        <v>58.797427075542259</v>
       </c>
       <c r="K61" s="1">
         <v>281.15932741279147</v>
@@ -5822,7 +5881,8 @@
         <v>314.74361642294718</v>
       </c>
       <c r="O61" s="1">
-        <v>2151.3682734426852</v>
+        <f t="shared" si="0"/>
+        <v>2054.6637415589053</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
@@ -5842,7 +5902,7 @@
         <v>44.021433178315625</v>
       </c>
       <c r="F62" s="1">
-        <v>106.86636148255231</v>
+        <v>98.317052563948124</v>
       </c>
       <c r="G62" s="1">
         <v>34.100257412527412</v>
@@ -5869,7 +5929,8 @@
         <v>85.732402980877396</v>
       </c>
       <c r="O62" s="1">
-        <v>1905.4661078979807</v>
+        <f t="shared" si="0"/>
+        <v>1872.7876825490198</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
@@ -5889,7 +5950,7 @@
         <v>204.09937200855427</v>
       </c>
       <c r="F63" s="1">
-        <v>275.44428382122635</v>
+        <v>253.40874111552824</v>
       </c>
       <c r="G63" s="1">
         <v>202.16581180284109</v>
@@ -5901,7 +5962,7 @@
         <v>195.3915356711004</v>
       </c>
       <c r="J63" s="1">
-        <v>-25.107596965487765</v>
+        <v>-23.098989208248746</v>
       </c>
       <c r="K63" s="1">
         <v>160.04454021958898</v>
@@ -5916,7 +5977,8 @@
         <v>90.430068897637796</v>
       </c>
       <c r="O63" s="1">
-        <v>1907.6715084858254</v>
+        <f t="shared" si="0"/>
+        <v>1939.8894855751596</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
@@ -5936,7 +5998,7 @@
         <v>436.21238331240033</v>
       </c>
       <c r="F64" s="1">
-        <v>183.62952254748424</v>
+        <v>168.93916074368551</v>
       </c>
       <c r="G64" s="1">
         <v>418.94601963962253</v>
@@ -5948,7 +6010,7 @@
         <v>302.04274889157603</v>
       </c>
       <c r="J64" s="1">
-        <v>20.542579335399083</v>
+        <v>18.899172988567155</v>
       </c>
       <c r="K64" s="1">
         <v>156.80039413405677</v>
@@ -5963,7 +6025,8 @@
         <v>25.837162542182231</v>
       </c>
       <c r="O64" s="1">
-        <v>1720.2124585190104</v>
+        <f t="shared" si="0"/>
+        <v>1712.7484751388222</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
@@ -6010,7 +6073,8 @@
         <v>0</v>
       </c>
       <c r="O65" s="1">
-        <v>1660.6666426471984</v>
+        <f t="shared" si="0"/>
+        <v>1678.8213298859114</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
@@ -6057,7 +6121,8 @@
         <v>234.88329583802027</v>
       </c>
       <c r="O66" s="1">
-        <v>1819.4554849720303</v>
+        <f t="shared" si="0"/>
+        <v>1665.844358122758</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
@@ -6077,7 +6142,7 @@
         <v>162.74590447740931</v>
       </c>
       <c r="F67" s="1">
-        <v>519.28020720395136</v>
+        <v>477.73779062763521</v>
       </c>
       <c r="G67" s="1">
         <v>91.339975212127001</v>
@@ -6089,7 +6154,7 @@
         <v>28.494598952035474</v>
       </c>
       <c r="J67" s="1">
-        <v>28.531360188054283</v>
+        <v>26.248851373009941</v>
       </c>
       <c r="K67" s="1">
         <v>295.21729378343105</v>
@@ -6104,7 +6169,8 @@
         <v>217.26704865016876</v>
       </c>
       <c r="O67" s="1">
-        <v>1780.8609746847446</v>
+        <f t="shared" ref="O67:O130" si="1">+SUM(C67:N67)</f>
+        <v>1837.1302189272576</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
@@ -6124,7 +6190,7 @@
         <v>228.11106283309007</v>
       </c>
       <c r="F68" s="1">
-        <v>216.74304300686666</v>
+        <v>199.40359956631733</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -6136,7 +6202,7 @@
         <v>159.56975413139864</v>
       </c>
       <c r="J68" s="1">
-        <v>69.616518858852444</v>
+        <v>64.047197350144245</v>
       </c>
       <c r="K68" s="1">
         <v>228.17160801576537</v>
@@ -6151,7 +6217,8 @@
         <v>151.49972581552308</v>
       </c>
       <c r="O68" s="1">
-        <v>1713.5962567554757</v>
+        <f t="shared" si="1"/>
+        <v>1708.8590319932982</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
@@ -6171,7 +6238,7 @@
         <v>787.04986591534009</v>
       </c>
       <c r="F69" s="1">
-        <v>12.041280167048146</v>
+        <v>11.077977753684294</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -6198,7 +6265,8 @@
         <v>89.25565241844771</v>
       </c>
       <c r="O69" s="1">
-        <v>1651.8450402958188</v>
+        <f t="shared" si="1"/>
+        <v>1721.2591792523644</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
@@ -6218,7 +6286,7 @@
         <v>73.369055297192716</v>
       </c>
       <c r="F70" s="1">
-        <v>385.32096534554069</v>
+        <v>354.49528811789742</v>
       </c>
       <c r="G70" s="1">
         <v>98.647173229097163</v>
@@ -6230,7 +6298,7 @@
         <v>320.76777106005648</v>
       </c>
       <c r="J70" s="1">
-        <v>280.74858425045409</v>
+        <v>258.28869751041776</v>
       </c>
       <c r="K70" s="1">
         <v>128.68446139277765</v>
@@ -6245,7 +6313,8 @@
         <v>72.813821709786282</v>
       </c>
       <c r="O70" s="1">
-        <v>1629.7910344173699</v>
+        <f t="shared" si="1"/>
+        <v>1592.168614321457</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
@@ -6265,7 +6334,7 @@
         <v>176.0857327132625</v>
       </c>
       <c r="F71" s="1">
-        <v>82.783801148456007</v>
+        <v>76.161097056579536</v>
       </c>
       <c r="G71" s="1">
         <v>334.91324244446565</v>
@@ -6292,7 +6361,8 @@
         <v>250.15071006749159</v>
       </c>
       <c r="O71" s="1">
-        <v>1765.4231705698305</v>
+        <f t="shared" si="1"/>
+        <v>1858.0716328297258</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
@@ -6312,7 +6382,7 @@
         <v>294.81020401235617</v>
       </c>
       <c r="F72" s="1">
-        <v>138.47472192105369</v>
+        <v>127.39674416736939</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
@@ -6339,7 +6409,8 @@
         <v>0</v>
       </c>
       <c r="O72" s="1">
-        <v>1422.4833791599508</v>
+        <f t="shared" si="1"/>
+        <v>1510.5803478923865</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
@@ -6359,7 +6430,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="1">
-        <v>317.58876440589489</v>
+        <v>292.18166325342327</v>
       </c>
       <c r="G73" s="1">
         <v>58.457584135761273</v>
@@ -6371,7 +6442,7 @@
         <v>90.368585247883928</v>
       </c>
       <c r="J73" s="1">
-        <v>22.825088150443424</v>
+        <v>20.999081098407949</v>
       </c>
       <c r="K73" s="1">
         <v>16.220730427661046</v>
@@ -6386,7 +6457,8 @@
         <v>399.30160292463449</v>
       </c>
       <c r="O73" s="1">
-        <v>1794.0933782118141</v>
+        <f t="shared" si="1"/>
+        <v>1751.644437525199</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
@@ -6406,7 +6478,7 @@
         <v>217.43920024440752</v>
       </c>
       <c r="F74" s="1">
-        <v>24.082560334096293</v>
+        <v>22.155955507368589</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -6433,7 +6505,8 @@
         <v>290.08087035995504</v>
       </c>
       <c r="O74" s="1">
-        <v>1672.7963458803454</v>
+        <f t="shared" si="1"/>
+        <v>1661.7452425488693</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
@@ -6453,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="1">
-        <v>144.49536200457777</v>
+        <v>132.93573304421153</v>
       </c>
       <c r="G75" s="1">
         <v>73.071980169701604</v>
@@ -6465,7 +6538,7 @@
         <v>115.60665860540105</v>
       </c>
       <c r="J75" s="1">
-        <v>79.887808526551979</v>
+        <v>73.496783844427824</v>
       </c>
       <c r="K75" s="1">
         <v>334.1470468098176</v>
@@ -6480,7 +6553,8 @@
         <v>109.22073256467942</v>
       </c>
       <c r="O75" s="1">
-        <v>1464.3859903290036</v>
+        <f t="shared" si="1"/>
+        <v>1394.7234155800816</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
@@ -6512,7 +6586,7 @@
         <v>392.41133413945988</v>
       </c>
       <c r="J76" s="1">
-        <v>117.54920397478364</v>
+        <v>108.14526765680094</v>
       </c>
       <c r="K76" s="1">
         <v>8.651056228085892</v>
@@ -6527,7 +6601,8 @@
         <v>164.41830708661419</v>
       </c>
       <c r="O76" s="1">
-        <v>1407.0455750450367</v>
+        <f t="shared" si="1"/>
+        <v>1284.3725403080398</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
@@ -6547,7 +6622,7 @@
         <v>129.39633388777622</v>
       </c>
       <c r="F77" s="1">
-        <v>91.814761273742121</v>
+        <v>84.469580371842753</v>
       </c>
       <c r="G77" s="1">
         <v>105.95437124606731</v>
@@ -6559,7 +6634,7 @@
         <v>102.58055622732769</v>
       </c>
       <c r="J77" s="1">
-        <v>110.7016775296506</v>
+        <v>101.84554332727856</v>
       </c>
       <c r="K77" s="1">
         <v>103.8126747370307</v>
@@ -6574,7 +6649,8 @@
         <v>204.34846737907762</v>
       </c>
       <c r="O77" s="1">
-        <v>1440.1265838627098</v>
+        <f t="shared" si="1"/>
+        <v>1460.0466394541113</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
@@ -6594,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>269.42364373770226</v>
+        <v>247.86975223868612</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -6606,7 +6682,7 @@
         <v>91.182716646513498</v>
       </c>
       <c r="J78" s="1">
-        <v>128.96174805000535</v>
+        <v>118.64480820600492</v>
       </c>
       <c r="K78" s="1">
         <v>220.60193381619021</v>
@@ -6621,7 +6697,8 @@
         <v>196.12755202474693</v>
       </c>
       <c r="O78" s="1">
-        <v>1392.7104712240448</v>
+        <f t="shared" si="1"/>
+        <v>1408.8083550494134</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
@@ -6668,7 +6745,8 @@
         <v>299.47620219347584</v>
       </c>
       <c r="O79" s="1">
-        <v>1455.5643879776242</v>
+        <f t="shared" si="1"/>
+        <v>1340.6343071662991</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
@@ -6688,7 +6766,7 @@
         <v>24.011690824535798</v>
       </c>
       <c r="F80" s="1">
-        <v>374.78484519937359</v>
+        <v>344.80205758342373</v>
       </c>
       <c r="G80" s="1">
         <v>136.40102965010965</v>
@@ -6700,7 +6778,7 @@
         <v>74.085957275292216</v>
       </c>
       <c r="J80" s="1">
-        <v>55.921465968586389</v>
+        <v>51.447748691099484</v>
       </c>
       <c r="K80" s="1">
         <v>30.278696798300619</v>
@@ -6715,7 +6793,8 @@
         <v>147.97647637795276</v>
       </c>
       <c r="O80" s="1">
-        <v>1296.7755456527923</v>
+        <f t="shared" si="1"/>
+        <v>1386.1288047904682</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
@@ -6762,7 +6841,8 @@
         <v>71.639405230596182</v>
       </c>
       <c r="O81" s="1">
-        <v>1222.8946259599886</v>
+        <f t="shared" si="1"/>
+        <v>1458.9630109532904</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
@@ -6809,7 +6889,8 @@
         <v>234.88329583802027</v>
       </c>
       <c r="O82" s="1">
-        <v>1362.937563288139</v>
+        <f t="shared" si="1"/>
+        <v>1451.6706136831117</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
@@ -6829,7 +6910,7 @@
         <v>-13.33982823585322</v>
       </c>
       <c r="F83" s="1">
-        <v>120.41280167048147</v>
+        <v>110.77977753684294</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
@@ -6856,7 +6937,8 @@
         <v>69.290572272215968</v>
       </c>
       <c r="O83" s="1">
-        <v>1205.2514212572296</v>
+        <f t="shared" si="1"/>
+        <v>1149.4008596594767</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
@@ -6903,7 +6985,8 @@
         <v>305.34828458942633</v>
       </c>
       <c r="O84" s="1">
-        <v>1402.6347738693469</v>
+        <f t="shared" si="1"/>
+        <v>1304.9968432003009</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
@@ -6923,7 +7006,7 @@
         <v>188.09157812553042</v>
       </c>
       <c r="F85" s="1">
-        <v>48.165120668192586</v>
+        <v>44.311911014737177</v>
       </c>
       <c r="G85" s="1">
         <v>192.42288111354753</v>
@@ -6935,7 +7018,7 @@
         <v>98.50989923417977</v>
       </c>
       <c r="J85" s="1">
-        <v>29.672614595576448</v>
+        <v>27.298805427930333</v>
       </c>
       <c r="K85" s="1">
         <v>21.627640570214727</v>
@@ -6950,7 +7033,8 @@
         <v>0</v>
       </c>
       <c r="O85" s="1">
-        <v>1100.4948933345977</v>
+        <f t="shared" si="1"/>
+        <v>1172.56266995433</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
@@ -6970,7 +7054,7 @@
         <v>242.78487389252862</v>
       </c>
       <c r="F86" s="1">
-        <v>322.10424446853796</v>
+        <v>296.33590491105491</v>
       </c>
       <c r="G86" s="1">
         <v>652.77635618266754</v>
@@ -6997,7 +7081,8 @@
         <v>0</v>
       </c>
       <c r="O86" s="1">
-        <v>1093.878691571063</v>
+        <f t="shared" si="1"/>
+        <v>1249.8544891468016</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
@@ -7017,7 +7102,7 @@
         <v>157.40997318306799</v>
       </c>
       <c r="F87" s="1">
-        <v>13.546440187929166</v>
+        <v>12.462724972894833</v>
       </c>
       <c r="G87" s="1">
         <v>219.21594050910477</v>
@@ -7029,7 +7114,7 @@
         <v>145.72952035469569</v>
       </c>
       <c r="J87" s="1">
-        <v>11.412544075221712</v>
+        <v>10.499540549203974</v>
       </c>
       <c r="K87" s="1">
         <v>71.371213881708599</v>
@@ -7044,7 +7129,8 @@
         <v>0</v>
       </c>
       <c r="O87" s="1">
-        <v>1092.7759912771405</v>
+        <f t="shared" si="1"/>
+        <v>1000.8568964360724</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
@@ -7064,7 +7150,7 @@
         <v>52.025330119827565</v>
       </c>
       <c r="F88" s="1">
-        <v>43.649640605549536</v>
+        <v>40.157669357105569</v>
       </c>
       <c r="G88" s="1">
         <v>149.79755934788827</v>
@@ -7091,7 +7177,8 @@
         <v>0</v>
       </c>
       <c r="O88" s="1">
-        <v>1086.159789513606</v>
+        <f t="shared" si="1"/>
+        <v>1071.6695706696776</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
@@ -7111,7 +7198,7 @@
         <v>321.48986048406266</v>
       </c>
       <c r="F89" s="1">
-        <v>31.608360438501386</v>
+        <v>29.079691603421274</v>
       </c>
       <c r="G89" s="1">
         <v>0</v>
@@ -7138,7 +7225,8 @@
         <v>0</v>
       </c>
       <c r="O89" s="1">
-        <v>1067.4138845169243</v>
+        <f t="shared" si="1"/>
+        <v>1078.8566925915341</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
@@ -7158,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="1">
-        <v>230.28948319479582</v>
+        <v>211.86632453921214</v>
       </c>
       <c r="G90" s="1">
         <v>153.45115835637336</v>
@@ -7185,7 +7273,8 @@
         <v>0</v>
       </c>
       <c r="O90" s="1">
-        <v>1061.9003830473123</v>
+        <f t="shared" si="1"/>
+        <v>1162.41434200767</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
@@ -7232,7 +7321,8 @@
         <v>0</v>
       </c>
       <c r="O91" s="1">
-        <v>1047.5652792263204</v>
+        <f t="shared" si="1"/>
+        <v>1223.8844978320944</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
@@ -7279,7 +7369,8 @@
         <v>0</v>
       </c>
       <c r="O92" s="1">
-        <v>1006.76536835119</v>
+        <f t="shared" si="1"/>
+        <v>999.2978142197652</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
@@ -7299,7 +7390,7 @@
         <v>114.7225228283377</v>
       </c>
       <c r="F93" s="1">
-        <v>96.330241336385171</v>
+        <v>88.623822029474354</v>
       </c>
       <c r="G93" s="1">
         <v>42.625321765659265</v>
@@ -7326,7 +7417,8 @@
         <v>0</v>
       </c>
       <c r="O93" s="1">
-        <v>1004.5599677633452</v>
+        <f t="shared" si="1"/>
+        <v>997.33940159407518</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
@@ -7346,7 +7438,7 @@
         <v>154.74200753589736</v>
       </c>
       <c r="F94" s="1">
-        <v>21.072240292334257</v>
+        <v>19.386461068947519</v>
       </c>
       <c r="G94" s="1">
         <v>252.09833158547053</v>
@@ -7373,7 +7465,8 @@
         <v>0</v>
       </c>
       <c r="O94" s="1">
-        <v>994.63566511804322</v>
+        <f t="shared" si="1"/>
+        <v>1099.0651489427862</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
@@ -7393,7 +7486,7 @@
         <v>285.47232424725894</v>
       </c>
       <c r="F95" s="1">
-        <v>141.48504196281573</v>
+        <v>130.16623860579045</v>
       </c>
       <c r="G95" s="1">
         <v>219.21594050910477</v>
@@ -7420,7 +7513,8 @@
         <v>0</v>
       </c>
       <c r="O95" s="1">
-        <v>992.4302645301982</v>
+        <f t="shared" si="1"/>
+        <v>1073.409776449545</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
@@ -7440,7 +7534,7 @@
         <v>36.0175362368037</v>
       </c>
       <c r="F96" s="1">
-        <v>165.56760229691201</v>
+        <v>152.32219411315907</v>
       </c>
       <c r="G96" s="1">
         <v>56.021851463437891</v>
@@ -7467,7 +7561,8 @@
         <v>0</v>
       </c>
       <c r="O96" s="1">
-        <v>986.91676306058616</v>
+        <f t="shared" si="1"/>
+        <v>968.11241693875968</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.35">
@@ -7487,7 +7582,7 @@
         <v>122.72641976984963</v>
       </c>
       <c r="F97" s="1">
-        <v>246.846243424487</v>
+        <v>227.09854395052804</v>
       </c>
       <c r="G97" s="1">
         <v>41.407455429497567</v>
@@ -7499,7 +7594,7 @@
         <v>174.22411930673118</v>
       </c>
       <c r="J97" s="1">
-        <v>5.706272037610856</v>
+        <v>5.2497702746019872</v>
       </c>
       <c r="K97" s="1">
         <v>0</v>
@@ -7514,7 +7609,8 @@
         <v>0</v>
       </c>
       <c r="O97" s="1">
-        <v>974.78705982743918</v>
+        <f t="shared" si="1"/>
+        <v>993.82363358807243</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.35">
@@ -7546,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="1">
-        <v>155.21059942301528</v>
+        <v>142.79375146917405</v>
       </c>
       <c r="K98" s="1">
         <v>0</v>
@@ -7561,7 +7657,8 @@
         <v>0</v>
       </c>
       <c r="O98" s="1">
-        <v>971.47895894567182</v>
+        <f t="shared" si="1"/>
+        <v>1087.4283209866771</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.35">
@@ -7581,7 +7678,7 @@
         <v>157.40997318306799</v>
       </c>
       <c r="F99" s="1">
-        <v>124.92828173312452</v>
+        <v>114.93401919447456</v>
       </c>
       <c r="G99" s="1">
         <v>58.457584135761273</v>
@@ -7593,7 +7690,7 @@
         <v>53.732672309552605</v>
       </c>
       <c r="J99" s="1">
-        <v>67.334010043808107</v>
+        <v>61.947289240303455</v>
       </c>
       <c r="K99" s="1">
         <v>86.510562280858906</v>
@@ -7608,7 +7705,8 @@
         <v>0</v>
       </c>
       <c r="O99" s="1">
-        <v>970.37625865174948</v>
+        <f t="shared" si="1"/>
+        <v>1043.1629957320679</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.35">
@@ -7655,7 +7753,8 @@
         <v>0</v>
       </c>
       <c r="O100" s="1">
-        <v>960.4519560064474</v>
+        <f t="shared" si="1"/>
+        <v>969.38658887336487</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.35">
@@ -7702,7 +7801,8 @@
         <v>0</v>
       </c>
       <c r="O101" s="1">
-        <v>954.93845453683525</v>
+        <f t="shared" si="1"/>
+        <v>982.34598031731866</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.35">
@@ -7722,7 +7822,7 @@
         <v>257.45868495196714</v>
       </c>
       <c r="F102" s="1">
-        <v>-60.206400835240736</v>
+        <v>-55.389888768421471</v>
       </c>
       <c r="G102" s="1">
         <v>0</v>
@@ -7734,7 +7834,7 @@
         <v>105.83708182184604</v>
       </c>
       <c r="J102" s="1">
-        <v>66.192755636285924</v>
+        <v>60.897335185383056</v>
       </c>
       <c r="K102" s="1">
         <v>101.64991068000923</v>
@@ -7749,7 +7849,8 @@
         <v>0</v>
       </c>
       <c r="O102" s="1">
-        <v>943.91145159761072</v>
+        <f t="shared" si="1"/>
+        <v>935.01034141215234</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.35">
@@ -7796,7 +7897,8 @@
         <v>0</v>
       </c>
       <c r="O103" s="1">
-        <v>937.29524983407623</v>
+        <f t="shared" si="1"/>
+        <v>807.26699743366919</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.35">
@@ -7816,7 +7918,7 @@
         <v>194.76149224345701</v>
       </c>
       <c r="F104" s="1">
-        <v>81.278641127574986</v>
+        <v>74.776349837368997</v>
       </c>
       <c r="G104" s="1">
         <v>0</v>
@@ -7828,7 +7930,7 @@
         <v>142.47299476017736</v>
       </c>
       <c r="J104" s="1">
-        <v>150.64558179292658</v>
+        <v>138.59393524949246</v>
       </c>
       <c r="K104" s="1">
         <v>135.17275356384204</v>
@@ -7843,7 +7945,8 @@
         <v>0</v>
       </c>
       <c r="O104" s="1">
-        <v>921.85744571916189</v>
+        <f t="shared" si="1"/>
+        <v>895.8053964091223</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.35">
@@ -7863,7 +7966,7 @@
         <v>84.040917885875288</v>
       </c>
       <c r="F105" s="1">
-        <v>215.23788298598561</v>
+        <v>198.01885234710676</v>
       </c>
       <c r="G105" s="1">
         <v>56.021851463437891</v>
@@ -7890,7 +7993,8 @@
         <v>0</v>
       </c>
       <c r="O105" s="1">
-        <v>921.85744571916189</v>
+        <f t="shared" si="1"/>
+        <v>916.20412320370804</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.35">
@@ -7910,7 +8014,7 @@
         <v>68.033124002851423</v>
       </c>
       <c r="F106" s="1">
-        <v>43.649640605549536</v>
+        <v>40.157669357105569</v>
       </c>
       <c r="G106" s="1">
         <v>0</v>
@@ -7937,7 +8041,8 @@
         <v>0</v>
       </c>
       <c r="O106" s="1">
-        <v>920.75474542523955</v>
+        <f t="shared" si="1"/>
+        <v>970.30600013168487</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.35">
@@ -7969,7 +8074,7 @@
         <v>25.238073357517134</v>
       </c>
       <c r="J107" s="1">
-        <v>164.34063468319266</v>
+        <v>151.19338390853724</v>
       </c>
       <c r="K107" s="1">
         <v>123.27755125022395</v>
@@ -7984,7 +8089,8 @@
         <v>0</v>
       </c>
       <c r="O107" s="1">
-        <v>913.03584336778249</v>
+        <f t="shared" si="1"/>
+        <v>976.31853703781348</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.35">
@@ -8031,7 +8137,8 @@
         <v>0</v>
       </c>
       <c r="O108" s="1">
-        <v>911.93314307385992</v>
+        <f t="shared" si="1"/>
+        <v>1068.4144855659254</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.35">
@@ -8063,7 +8170,7 @@
         <v>79.78487706569932</v>
       </c>
       <c r="J109" s="1">
-        <v>30.81386900309862</v>
+        <v>28.348759482850731</v>
       </c>
       <c r="K109" s="1">
         <v>0</v>
@@ -8078,7 +8185,8 @@
         <v>0</v>
       </c>
       <c r="O109" s="1">
-        <v>904.21424101640287</v>
+        <f t="shared" si="1"/>
+        <v>984.68510052415388</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.35">
@@ -8098,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="1">
-        <v>209.21724290246155</v>
+        <v>192.4798634702646</v>
       </c>
       <c r="G110" s="1">
         <v>69.418381161216516</v>
@@ -8125,7 +8233,8 @@
         <v>0</v>
       </c>
       <c r="O110" s="1">
-        <v>883.26293543187637</v>
+        <f t="shared" si="1"/>
+        <v>897.93692138351196</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.35">
@@ -8157,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="1">
-        <v>14.836307297788224</v>
+        <v>13.649402713965166</v>
       </c>
       <c r="K111" s="1">
         <v>110.30096690809511</v>
@@ -8172,7 +8281,8 @@
         <v>0</v>
       </c>
       <c r="O111" s="1">
-        <v>883.26293543187637</v>
+        <f t="shared" si="1"/>
+        <v>936.86504478183383</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.35">
@@ -8192,7 +8302,7 @@
         <v>137.40023082928818</v>
       </c>
       <c r="F112" s="1">
-        <v>126.43344175400554</v>
+        <v>116.3187664136851</v>
       </c>
       <c r="G112" s="1">
         <v>0</v>
@@ -8204,7 +8314,7 @@
         <v>89.554453849254344</v>
       </c>
       <c r="J112" s="1">
-        <v>132.38551127257185</v>
+        <v>121.79467037076611</v>
       </c>
       <c r="K112" s="1">
         <v>114.62649502213806</v>
@@ -8219,7 +8329,8 @@
         <v>0</v>
       </c>
       <c r="O112" s="1">
-        <v>870.03053190480716</v>
+        <f t="shared" si="1"/>
+        <v>845.52180420441323</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.35">
@@ -8266,7 +8377,8 @@
         <v>0</v>
       </c>
       <c r="O113" s="1">
-        <v>868.9278316108846</v>
+        <f t="shared" si="1"/>
+        <v>688.12947641264896</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.35">
@@ -8313,7 +8425,8 @@
         <v>0</v>
       </c>
       <c r="O114" s="1">
-        <v>862.31162984734999</v>
+        <f t="shared" si="1"/>
+        <v>790.4580453853448</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.35">
@@ -8333,7 +8446,7 @@
         <v>146.73811059438543</v>
       </c>
       <c r="F115" s="1">
-        <v>109.87668152431435</v>
+        <v>101.0865470023692</v>
       </c>
       <c r="G115" s="1">
         <v>0</v>
@@ -8345,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="1">
-        <v>102.71289667699541</v>
+        <v>94.49586494283578</v>
       </c>
       <c r="K115" s="1">
         <v>92.998854451923336</v>
@@ -8360,7 +8473,8 @@
         <v>0</v>
       </c>
       <c r="O115" s="1">
-        <v>853.49002749597048</v>
+        <f t="shared" si="1"/>
+        <v>923.40894184379511</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.35">
@@ -8380,7 +8494,7 @@
         <v>44.021433178315625</v>
       </c>
       <c r="F116" s="1">
-        <v>39.134160542906478</v>
+        <v>36.00342769947396</v>
       </c>
       <c r="G116" s="1">
         <v>29.228792067880637</v>
@@ -8407,7 +8521,8 @@
         <v>0</v>
       </c>
       <c r="O116" s="1">
-        <v>851.28462690812557</v>
+        <f t="shared" si="1"/>
+        <v>739.72214855961454</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.35">
@@ -8427,7 +8542,7 @@
         <v>53.359312943412881</v>
       </c>
       <c r="F117" s="1">
-        <v>55.690920772597678</v>
+        <v>51.23564711078987</v>
       </c>
       <c r="G117" s="1">
         <v>65.764782152731442</v>
@@ -8454,7 +8569,8 @@
         <v>0</v>
       </c>
       <c r="O117" s="1">
-        <v>843.56572485066852</v>
+        <f t="shared" si="1"/>
+        <v>754.27898132426185</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.35">
@@ -8474,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="1">
-        <v>189.6501626310083</v>
+        <v>174.47814962052763</v>
       </c>
       <c r="G118" s="1">
         <v>31.664524740204026</v>
@@ -8486,7 +8602,7 @@
         <v>126.19036678758566</v>
       </c>
       <c r="J118" s="1">
-        <v>19.40132492787691</v>
+        <v>17.849218933646757</v>
       </c>
       <c r="K118" s="1">
         <v>0</v>
@@ -8501,7 +8617,8 @@
         <v>0</v>
       </c>
       <c r="O118" s="1">
-        <v>817.10091779652987</v>
+        <f t="shared" si="1"/>
+        <v>840.38425632246697</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.35">
@@ -8521,7 +8638,7 @@
         <v>16.007793883023865</v>
       </c>
       <c r="F119" s="1">
-        <v>117.40248162871943</v>
+        <v>108.01028309842188</v>
       </c>
       <c r="G119" s="1">
         <v>66.982648488893133</v>
@@ -8548,7 +8665,8 @@
         <v>0</v>
       </c>
       <c r="O119" s="1">
-        <v>791.73881103631368</v>
+        <f t="shared" si="1"/>
+        <v>730.15731335734881</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.35">
@@ -8568,7 +8686,7 @@
         <v>73.369055297192716</v>
       </c>
       <c r="F120" s="1">
-        <v>61.71156085612175</v>
+        <v>56.77463598763201</v>
       </c>
       <c r="G120" s="1">
         <v>82.814910858995134</v>
@@ -8595,7 +8713,8 @@
         <v>0</v>
       </c>
       <c r="O120" s="1">
-        <v>788.43071015454643</v>
+        <f t="shared" si="1"/>
+        <v>809.83749704893137</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.35">
@@ -8642,7 +8761,8 @@
         <v>0</v>
       </c>
       <c r="O121" s="1">
-        <v>778.50640750924435</v>
+        <f t="shared" si="1"/>
+        <v>672.38331668536432</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.35">
@@ -8662,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="1">
-        <v>213.73272296510461</v>
+        <v>196.63410512789625</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
@@ -8689,7 +8809,8 @@
         <v>0</v>
       </c>
       <c r="O122" s="1">
-        <v>777.40370721532202</v>
+        <f t="shared" si="1"/>
+        <v>852.5136258617232</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.35">
@@ -8709,7 +8830,7 @@
         <v>64.03117553209546</v>
       </c>
       <c r="F123" s="1">
-        <v>22.577400313215275</v>
+        <v>20.771208288158054</v>
       </c>
       <c r="G123" s="1">
         <v>0</v>
@@ -8736,7 +8857,8 @@
         <v>0</v>
       </c>
       <c r="O123" s="1">
-        <v>770.7875054517873</v>
+        <f t="shared" si="1"/>
+        <v>669.42329332465647</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.35">
@@ -8783,7 +8905,8 @@
         <v>0</v>
       </c>
       <c r="O124" s="1">
-        <v>760.86320280648533</v>
+        <f t="shared" si="1"/>
+        <v>674.28868286600016</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.35">
@@ -8803,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="1">
-        <v>394.35192547082681</v>
+        <v>362.8037714331607</v>
       </c>
       <c r="G125" s="1">
         <v>0</v>
@@ -8830,7 +8953,8 @@
         <v>0</v>
       </c>
       <c r="O125" s="1">
-        <v>759.76050251256288</v>
+        <f t="shared" si="1"/>
+        <v>815.22935308639467</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.35">
@@ -8850,7 +8974,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="1">
-        <v>118.90764164960045</v>
+        <v>109.39503031763242</v>
       </c>
       <c r="G126" s="1">
         <v>0</v>
@@ -8877,7 +9001,8 @@
         <v>0</v>
       </c>
       <c r="O126" s="1">
-        <v>747.63079927941601</v>
+        <f t="shared" si="1"/>
+        <v>947.84462944485585</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.35">
@@ -8924,7 +9049,8 @@
         <v>0</v>
       </c>
       <c r="O127" s="1">
-        <v>741.01459751588129</v>
+        <f t="shared" si="1"/>
+        <v>746.05158700861</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.35">
@@ -8971,7 +9097,8 @@
         <v>0</v>
       </c>
       <c r="O128" s="1">
-        <v>735.50109604626914</v>
+        <f t="shared" si="1"/>
+        <v>671.23210391233556</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.35">
@@ -8991,7 +9118,7 @@
         <v>46.689398825486272</v>
       </c>
       <c r="F129" s="1">
-        <v>126.43344175400554</v>
+        <v>116.3187664136851</v>
       </c>
       <c r="G129" s="1">
         <v>96.211440556773766</v>
@@ -9003,7 +9130,7 @@
         <v>96.881636436920601</v>
       </c>
       <c r="J129" s="1">
-        <v>55.921465968586389</v>
+        <v>51.447748691099484</v>
       </c>
       <c r="K129" s="1">
         <v>0</v>
@@ -9018,7 +9145,8 @@
         <v>0</v>
       </c>
       <c r="O129" s="1">
-        <v>717.85789134351</v>
+        <f t="shared" si="1"/>
+        <v>745.8538871367374</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.35">
@@ -9050,7 +9178,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="1">
-        <v>232.81589913452291</v>
+        <v>214.19062720376107</v>
       </c>
       <c r="K130" s="1">
         <v>3.2441460855322095</v>
@@ -9065,7 +9193,8 @@
         <v>0</v>
       </c>
       <c r="O130" s="1">
-        <v>715.65249075566521</v>
+        <f t="shared" si="1"/>
+        <v>735.99351263507447</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.35">
@@ -9085,7 +9214,7 @@
         <v>125.39438541702026</v>
       </c>
       <c r="F131" s="1">
-        <v>75.258001044050914</v>
+        <v>69.237360960526843</v>
       </c>
       <c r="G131" s="1">
         <v>166.84768805415197</v>
@@ -9097,7 +9226,7 @@
         <v>48.8478839177751</v>
       </c>
       <c r="J131" s="1">
-        <v>-35.378886633187307</v>
+        <v>-32.548575702532325</v>
       </c>
       <c r="K131" s="1">
         <v>33.52284288383283</v>
@@ -9112,7 +9241,8 @@
         <v>0</v>
       </c>
       <c r="O131" s="1">
-        <v>711.2416895799754</v>
+        <f t="shared" ref="O131:O194" si="2">+SUM(C131:N131)</f>
+        <v>735.80995316701467</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.35">
@@ -9159,7 +9289,8 @@
         <v>0</v>
       </c>
       <c r="O132" s="1">
-        <v>706.8308884042857</v>
+        <f t="shared" si="2"/>
+        <v>628.57183803677719</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.35">
@@ -9206,7 +9337,8 @@
         <v>0</v>
       </c>
       <c r="O133" s="1">
-        <v>692.49578458329393</v>
+        <f t="shared" si="2"/>
+        <v>591.93068376384201</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.35">
@@ -9226,7 +9358,7 @@
         <v>268.13054754064973</v>
       </c>
       <c r="F134" s="1">
-        <v>82.783801148456007</v>
+        <v>76.161097056579536</v>
       </c>
       <c r="G134" s="1">
         <v>51.150386118791111</v>
@@ -9238,7 +9370,7 @@
         <v>55.360935106811773</v>
       </c>
       <c r="J134" s="1">
-        <v>25.107596965487765</v>
+        <v>23.098989208248746</v>
       </c>
       <c r="K134" s="1">
         <v>44.336663168940191</v>
@@ -9253,7 +9385,8 @@
         <v>0</v>
       </c>
       <c r="O134" s="1">
-        <v>685.87958281975921</v>
+        <f t="shared" si="2"/>
+        <v>745.60691531978705</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.35">
@@ -9273,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="1">
-        <v>30.103200417620368</v>
+        <v>27.694944384210736</v>
       </c>
       <c r="G135" s="1">
         <v>0</v>
@@ -9300,7 +9433,8 @@
         <v>0</v>
       </c>
       <c r="O135" s="1">
-        <v>685.87958281975921</v>
+        <f t="shared" si="2"/>
+        <v>702.32063744568325</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.35">
@@ -9347,7 +9481,8 @@
         <v>0</v>
       </c>
       <c r="O136" s="1">
-        <v>683.67418223191441</v>
+        <f t="shared" si="2"/>
+        <v>636.54545264922149</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.35">
@@ -9394,7 +9529,8 @@
         <v>0</v>
       </c>
       <c r="O137" s="1">
-        <v>679.26338105622449</v>
+        <f t="shared" si="2"/>
+        <v>570.5106436155221</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.35">
@@ -9414,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="F138" s="1">
-        <v>230.28948319479582</v>
+        <v>211.86632453921214</v>
       </c>
       <c r="G138" s="1">
         <v>51.150386118791111</v>
@@ -9441,7 +9577,8 @@
         <v>0</v>
       </c>
       <c r="O138" s="1">
-        <v>674.85257988053479</v>
+        <f t="shared" si="2"/>
+        <v>672.35920584758776</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.35">
@@ -9488,7 +9625,8 @@
         <v>0</v>
       </c>
       <c r="O139" s="1">
-        <v>673.74987958661234</v>
+        <f t="shared" si="2"/>
+        <v>544.98708039723851</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.35">
@@ -9508,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="1">
-        <v>118.90764164960045</v>
+        <v>109.39503031763242</v>
       </c>
       <c r="G140" s="1">
         <v>523.68252454952813</v>
@@ -9535,7 +9673,8 @@
         <v>0</v>
       </c>
       <c r="O140" s="1">
-        <v>671.54447899876743</v>
+        <f t="shared" si="2"/>
+        <v>669.89369948595288</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.35">
@@ -9555,7 +9694,7 @@
         <v>70.70108965002207</v>
       </c>
       <c r="F141" s="1">
-        <v>99.340561378147214</v>
+        <v>91.393316467895431</v>
       </c>
       <c r="G141" s="1">
         <v>3.6535990084850796</v>
@@ -9567,7 +9706,7 @@
         <v>157.12735993550987</v>
       </c>
       <c r="J141" s="1">
-        <v>22.825088150443424</v>
+        <v>20.999081098407949</v>
       </c>
       <c r="K141" s="1">
         <v>34.604224912343568</v>
@@ -9582,7 +9721,8 @@
         <v>0</v>
       </c>
       <c r="O141" s="1">
-        <v>651.6958737081635</v>
+        <f t="shared" si="2"/>
+        <v>644.41153446182511</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.35">
@@ -9602,7 +9742,7 @@
         <v>42.687450354730309</v>
       </c>
       <c r="F142" s="1">
-        <v>493.692486848974</v>
+        <v>454.19708790105608</v>
       </c>
       <c r="G142" s="1">
         <v>0</v>
@@ -9629,7 +9769,8 @@
         <v>0</v>
       </c>
       <c r="O142" s="1">
-        <v>647.28507253247369</v>
+        <f t="shared" si="2"/>
+        <v>755.76241158106211</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.35">
@@ -9676,7 +9817,8 @@
         <v>0</v>
       </c>
       <c r="O143" s="1">
-        <v>637.36076988717184</v>
+        <f t="shared" si="2"/>
+        <v>470.56794840790008</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.35">
@@ -9723,7 +9865,8 @@
         <v>0</v>
       </c>
       <c r="O144" s="1">
-        <v>616.40946430264535</v>
+        <f t="shared" si="2"/>
+        <v>522.17762126829155</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.35">
@@ -9770,7 +9913,8 @@
         <v>0</v>
       </c>
       <c r="O145" s="1">
-        <v>577.81495401535983</v>
+        <f t="shared" si="2"/>
+        <v>471.99758271866102</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.35">
@@ -9790,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="1">
-        <v>189.6501626310083</v>
+        <v>174.47814962052763</v>
       </c>
       <c r="G146" s="1">
         <v>0</v>
@@ -9817,7 +9961,8 @@
         <v>0</v>
       </c>
       <c r="O146" s="1">
-        <v>576.71225372143749</v>
+        <f t="shared" si="2"/>
+        <v>539.7326198876641</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.35">
@@ -9864,7 +10009,8 @@
         <v>0</v>
       </c>
       <c r="O147" s="1">
-        <v>574.50685313359247</v>
+        <f t="shared" si="2"/>
+        <v>465.80203905183862</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.35">
@@ -9884,7 +10030,7 @@
         <v>24.011690824535798</v>
       </c>
       <c r="F148" s="1">
-        <v>124.92828173312452</v>
+        <v>114.93401919447456</v>
       </c>
       <c r="G148" s="1">
         <v>25.575193059395556</v>
@@ -9911,7 +10057,8 @@
         <v>0</v>
       </c>
       <c r="O148" s="1">
-        <v>572.30145254574768</v>
+        <f t="shared" si="2"/>
+        <v>647.79203849159467</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.35">
@@ -9958,7 +10105,8 @@
         <v>0</v>
       </c>
       <c r="O149" s="1">
-        <v>567.89065137005798</v>
+        <f t="shared" si="2"/>
+        <v>694.5461051785893</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.35">
@@ -9990,7 +10138,7 @@
         <v>137.58820636839985</v>
       </c>
       <c r="J150" s="1">
-        <v>142.65680094027138</v>
+        <v>131.24425686504969</v>
       </c>
       <c r="K150" s="1">
         <v>-4.325528114042946</v>
@@ -10005,7 +10153,8 @@
         <v>0</v>
       </c>
       <c r="O150" s="1">
-        <v>543.63124490376413</v>
+        <f t="shared" si="2"/>
+        <v>567.22629942258504</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.35">
@@ -10052,7 +10201,8 @@
         <v>0</v>
       </c>
       <c r="O151" s="1">
-        <v>542.52854460984167</v>
+        <f t="shared" si="2"/>
+        <v>465.45855771525294</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.35">
@@ -10072,7 +10222,7 @@
         <v>50.691347296242235</v>
       </c>
       <c r="F152" s="1">
-        <v>93.319921294623143</v>
+        <v>85.854327591053291</v>
       </c>
       <c r="G152" s="1">
         <v>91.339975212127001</v>
@@ -10099,7 +10249,8 @@
         <v>0</v>
       </c>
       <c r="O152" s="1">
-        <v>535.91234284630707</v>
+        <f t="shared" si="2"/>
+        <v>522.33454811802562</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.35">
@@ -10146,7 +10297,8 @@
         <v>0</v>
       </c>
       <c r="O153" s="1">
-        <v>532.60424196453971</v>
+        <f t="shared" si="2"/>
+        <v>616.11272252211916</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.35">
@@ -10166,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="1">
-        <v>388.33128538730273</v>
+        <v>357.26478255631855</v>
       </c>
       <c r="G154" s="1">
         <v>0</v>
@@ -10193,7 +10345,8 @@
         <v>0</v>
       </c>
       <c r="O154" s="1">
-        <v>531.50154167061726</v>
+        <f t="shared" si="2"/>
+        <v>586.26522104596529</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.35">
@@ -10240,7 +10393,8 @@
         <v>0</v>
       </c>
       <c r="O155" s="1">
-        <v>520.47453873139284</v>
+        <f t="shared" si="2"/>
+        <v>462.1682596045589</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.35">
@@ -10260,7 +10414,7 @@
         <v>28.013639295291764</v>
       </c>
       <c r="F156" s="1">
-        <v>27.092880375858332</v>
+        <v>24.925449945789666</v>
       </c>
       <c r="G156" s="1">
         <v>105.95437124606731</v>
@@ -10272,7 +10426,7 @@
         <v>19.539153567110038</v>
       </c>
       <c r="J156" s="1">
-        <v>23.966342557965593</v>
+        <v>22.049035153328347</v>
       </c>
       <c r="K156" s="1">
         <v>140.57966370639573</v>
@@ -10287,7 +10441,8 @@
         <v>0</v>
       </c>
       <c r="O156" s="1">
-        <v>518.26913814354805</v>
+        <f t="shared" si="2"/>
+        <v>506.07377742645565</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.35">
@@ -10334,7 +10489,8 @@
         <v>0</v>
       </c>
       <c r="O157" s="1">
-        <v>518.26913814354805</v>
+        <f t="shared" si="2"/>
+        <v>581.22817989256134</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.35">
@@ -10354,7 +10510,7 @@
         <v>28.013639295291764</v>
       </c>
       <c r="F158" s="1">
-        <v>33.113520459382407</v>
+        <v>30.464438822631813</v>
       </c>
       <c r="G158" s="1">
         <v>24.357326723233864</v>
@@ -10366,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="1">
-        <v>51.356448338497707</v>
+        <v>47.24793247141789</v>
       </c>
       <c r="K158" s="1">
         <v>32.441460855322092</v>
@@ -10381,7 +10537,8 @@
         <v>0</v>
       </c>
       <c r="O158" s="1">
-        <v>517.16643784962559</v>
+        <f t="shared" si="2"/>
+        <v>476.33680115277548</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.35">
@@ -10401,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="1">
-        <v>177.60888246396019</v>
+        <v>163.40017186684335</v>
       </c>
       <c r="G159" s="1">
         <v>0</v>
@@ -10428,7 +10585,8 @@
         <v>0</v>
       </c>
       <c r="O159" s="1">
-        <v>506.13943491040112</v>
+        <f t="shared" si="2"/>
+        <v>533.34500759104662</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.35">
@@ -10475,7 +10633,8 @@
         <v>0</v>
       </c>
       <c r="O160" s="1">
-        <v>486.29082961979719</v>
+        <f t="shared" si="2"/>
+        <v>448.26655931794772</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.35">
@@ -10522,7 +10681,8 @@
         <v>0</v>
       </c>
       <c r="O161" s="1">
-        <v>486.29082961979719</v>
+        <f t="shared" si="2"/>
+        <v>536.15486640049335</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.35">
@@ -10542,7 +10702,7 @@
         <v>10.671862588682577</v>
       </c>
       <c r="F162" s="1">
-        <v>114.39216158695739</v>
+        <v>105.2407886600008</v>
       </c>
       <c r="G162" s="1">
         <v>13.396529697778625</v>
@@ -10569,7 +10729,8 @@
         <v>0</v>
       </c>
       <c r="O162" s="1">
-        <v>479.67462785626253</v>
+        <f t="shared" si="2"/>
+        <v>474.91266227061368</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.35">
@@ -10589,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="F163" s="1">
-        <v>84.288961169337028</v>
+        <v>77.545844275790074</v>
       </c>
       <c r="G163" s="1">
         <v>0</v>
@@ -10616,7 +10777,8 @@
         <v>0</v>
       </c>
       <c r="O163" s="1">
-        <v>475.26382668057272</v>
+        <f t="shared" si="2"/>
+        <v>636.75649261910007</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.35">
@@ -10636,7 +10798,7 @@
         <v>0</v>
       </c>
       <c r="F164" s="1">
-        <v>136.96956190017266</v>
+        <v>126.01199694815885</v>
       </c>
       <c r="G164" s="1">
         <v>0</v>
@@ -10663,7 +10825,8 @@
         <v>0</v>
       </c>
       <c r="O164" s="1">
-        <v>465.33952403527076</v>
+        <f t="shared" si="2"/>
+        <v>445.12167771424623</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.35">
@@ -10710,7 +10873,8 @@
         <v>0</v>
       </c>
       <c r="O165" s="1">
-        <v>462.03142315350345</v>
+        <f t="shared" si="2"/>
+        <v>497.70621507721177</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.35">
@@ -10730,7 +10894,7 @@
         <v>-1.3339828235853222</v>
       </c>
       <c r="F166" s="1">
-        <v>22.577400313215275</v>
+        <v>20.771208288158054</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -10757,7 +10921,8 @@
         <v>0</v>
       </c>
       <c r="O166" s="1">
-        <v>460.92872285958094</v>
+        <f t="shared" si="2"/>
+        <v>501.32263242032531</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.35">
@@ -10777,7 +10942,7 @@
         <v>28.013639295291764</v>
       </c>
       <c r="F167" s="1">
-        <v>106.86636148255231</v>
+        <v>98.317052563948124</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -10804,7 +10969,8 @@
         <v>0</v>
       </c>
       <c r="O167" s="1">
-        <v>437.77201668720966</v>
+        <f t="shared" si="2"/>
+        <v>476.23268966207127</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.35">
@@ -10851,7 +11017,8 @@
         <v>0</v>
       </c>
       <c r="O168" s="1">
-        <v>435.56661609936481</v>
+        <f t="shared" si="2"/>
+        <v>359.54246300978895</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.35">
@@ -10871,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="1">
-        <v>112.88700156607638</v>
+        <v>103.85604144079028</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -10898,7 +11065,8 @@
         <v>0</v>
       </c>
       <c r="O169" s="1">
-        <v>435.56661609936481</v>
+        <f t="shared" si="2"/>
+        <v>385.82186371320319</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.35">
@@ -10945,7 +11113,8 @@
         <v>0</v>
       </c>
       <c r="O170" s="1">
-        <v>432.25851521759745</v>
+        <f t="shared" si="2"/>
+        <v>398.94984583587654</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.35">
@@ -10977,7 +11146,7 @@
         <v>36.635912938331323</v>
       </c>
       <c r="J171" s="1">
-        <v>30.81386900309862</v>
+        <v>28.348759482850731</v>
       </c>
       <c r="K171" s="1">
         <v>49.743573311493883</v>
@@ -10992,7 +11161,8 @@
         <v>0</v>
       </c>
       <c r="O171" s="1">
-        <v>428.95041433583015</v>
+        <f t="shared" si="2"/>
+        <v>417.0931872472687</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.35">
@@ -11039,7 +11209,8 @@
         <v>0</v>
       </c>
       <c r="O172" s="1">
-        <v>428.95041433583015</v>
+        <f t="shared" si="2"/>
+        <v>373.52088957795536</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.35">
@@ -11059,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="1">
-        <v>16.556760229691204</v>
+        <v>15.232219411315906</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -11086,7 +11257,8 @@
         <v>0</v>
       </c>
       <c r="O173" s="1">
-        <v>427.84771404190775</v>
+        <f t="shared" si="2"/>
+        <v>383.66189826019354</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.35">
@@ -11118,7 +11290,7 @@
         <v>26.866336154776302</v>
       </c>
       <c r="J174" s="1">
-        <v>20.542579335399083</v>
+        <v>18.899172988567155</v>
       </c>
       <c r="K174" s="1">
         <v>84.347798223837444</v>
@@ -11133,7 +11305,8 @@
         <v>0</v>
       </c>
       <c r="O174" s="1">
-        <v>427.84771404190775</v>
+        <f t="shared" si="2"/>
+        <v>438.68554449426455</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.35">
@@ -11165,7 +11338,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="1">
-        <v>55.921465968586389</v>
+        <v>51.447748691099484</v>
       </c>
       <c r="K175" s="1">
         <v>141.66104573490648</v>
@@ -11180,7 +11353,8 @@
         <v>0</v>
       </c>
       <c r="O175" s="1">
-        <v>425.64231345406279</v>
+        <f t="shared" si="2"/>
+        <v>481.24650816287186</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.35">
@@ -11227,7 +11401,8 @@
         <v>0</v>
       </c>
       <c r="O176" s="1">
-        <v>425.64231345406279</v>
+        <f t="shared" si="2"/>
+        <v>422.31159513453395</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.35">
@@ -11274,7 +11449,8 @@
         <v>0</v>
       </c>
       <c r="O177" s="1">
-        <v>421.23151227837303</v>
+        <f t="shared" si="2"/>
+        <v>327.20281027228816</v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.35">
@@ -11306,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="1">
-        <v>231.67464472700073</v>
+        <v>213.14067314884068</v>
       </c>
       <c r="K178" s="1">
         <v>54.069101425536822</v>
@@ -11321,7 +11497,8 @@
         <v>0</v>
       </c>
       <c r="O178" s="1">
-        <v>417.92341139660573</v>
+        <f t="shared" si="2"/>
+        <v>391.42685982044202</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.35">
@@ -11368,7 +11545,8 @@
         <v>0</v>
       </c>
       <c r="O179" s="1">
-        <v>417.92341139660573</v>
+        <f t="shared" si="2"/>
+        <v>341.54019828956109</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.35">
@@ -11415,7 +11593,8 @@
         <v>0</v>
       </c>
       <c r="O180" s="1">
-        <v>407.99910875130377</v>
+        <f t="shared" si="2"/>
+        <v>420.47220438122946</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.35">
@@ -11462,7 +11641,8 @@
         <v>0</v>
       </c>
       <c r="O181" s="1">
-        <v>404.69100786953641</v>
+        <f t="shared" si="2"/>
+        <v>320.4866977708657</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.35">
@@ -11482,7 +11662,7 @@
         <v>85.374900709460618</v>
       </c>
       <c r="F182" s="1">
-        <v>12.041280167048146</v>
+        <v>11.077977753684294</v>
       </c>
       <c r="G182" s="1">
         <v>0</v>
@@ -11509,7 +11689,8 @@
         <v>0</v>
       </c>
       <c r="O182" s="1">
-        <v>404.69100786953641</v>
+        <f t="shared" si="2"/>
+        <v>404.59871829735368</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.35">
@@ -11556,7 +11737,8 @@
         <v>0</v>
       </c>
       <c r="O183" s="1">
-        <v>398.07480610600174</v>
+        <f t="shared" si="2"/>
+        <v>428.61246499331253</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.35">
@@ -11603,7 +11785,8 @@
         <v>0</v>
       </c>
       <c r="O184" s="1">
-        <v>395.86940551815684</v>
+        <f t="shared" si="2"/>
+        <v>435.45206787760986</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.35">
@@ -11635,7 +11818,7 @@
         <v>13.840233776702943</v>
       </c>
       <c r="J185" s="1">
-        <v>149.50432738540442</v>
+        <v>137.54398119457207</v>
       </c>
       <c r="K185" s="1">
         <v>27.034550712768411</v>
@@ -11650,7 +11833,8 @@
         <v>0</v>
       </c>
       <c r="O185" s="1">
-        <v>382.63700199108757</v>
+        <f t="shared" si="2"/>
+        <v>376.50240925227632</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.35">
@@ -11697,7 +11881,8 @@
         <v>0</v>
       </c>
       <c r="O186" s="1">
-        <v>380.43160140324267</v>
+        <f t="shared" si="2"/>
+        <v>309.48303964720486</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.35">
@@ -11744,7 +11929,8 @@
         <v>0</v>
       </c>
       <c r="O187" s="1">
-        <v>379.32890110932021</v>
+        <f t="shared" si="2"/>
+        <v>346.41798729619705</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.35">
@@ -11791,7 +11977,8 @@
         <v>0</v>
       </c>
       <c r="O188" s="1">
-        <v>376.02080022755291</v>
+        <f t="shared" si="2"/>
+        <v>349.22595690414198</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.35">
@@ -11823,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="J189" s="1">
-        <v>89.017843786729344</v>
+        <v>81.896416283790998</v>
       </c>
       <c r="K189" s="1">
         <v>160.04454021958898</v>
@@ -11838,7 +12025,8 @@
         <v>0</v>
       </c>
       <c r="O189" s="1">
-        <v>371.60999905186316</v>
+        <f t="shared" si="2"/>
+        <v>394.11842503240558</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.35">
@@ -11858,7 +12046,7 @@
         <v>48.023381649071595</v>
       </c>
       <c r="F190" s="1">
-        <v>34.618680480263421</v>
+        <v>31.849186041842348</v>
       </c>
       <c r="G190" s="1">
         <v>7.3071980169701591</v>
@@ -11885,7 +12073,8 @@
         <v>0</v>
       </c>
       <c r="O190" s="1">
-        <v>366.09649758225089</v>
+        <f t="shared" si="2"/>
+        <v>353.63121177133166</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.35">
@@ -11905,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="F191" s="1">
-        <v>48.165120668192586</v>
+        <v>44.311911014737177</v>
       </c>
       <c r="G191" s="1">
         <v>0</v>
@@ -11917,7 +12106,7 @@
         <v>56.175066505441357</v>
       </c>
       <c r="J191" s="1">
-        <v>1.1412544075221713</v>
+        <v>1.0499540549203976</v>
       </c>
       <c r="K191" s="1">
         <v>42.173899111918722</v>
@@ -11932,7 +12121,8 @@
         <v>0</v>
       </c>
       <c r="O191" s="1">
-        <v>360.58299611263868</v>
+        <f t="shared" si="2"/>
+        <v>343.08494127742807</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.35">
@@ -11952,7 +12142,7 @@
         <v>38.685501883974339</v>
       </c>
       <c r="F192" s="1">
-        <v>24.082560334096293</v>
+        <v>22.155955507368589</v>
       </c>
       <c r="G192" s="1">
         <v>48.714653446467729</v>
@@ -11979,7 +12169,8 @@
         <v>0</v>
       </c>
       <c r="O192" s="1">
-        <v>358.37759552479383</v>
+        <f t="shared" si="2"/>
+        <v>379.86556502053975</v>
       </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.35">
@@ -12026,7 +12217,8 @@
         <v>0</v>
       </c>
       <c r="O193" s="1">
-        <v>350.65869346733672</v>
+        <f t="shared" si="2"/>
+        <v>332.99583465689432</v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.35">
@@ -12073,7 +12265,8 @@
         <v>0</v>
       </c>
       <c r="O194" s="1">
-        <v>350.65869346733672</v>
+        <f t="shared" si="2"/>
+        <v>319.14963367046801</v>
       </c>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.35">
@@ -12120,7 +12313,8 @@
         <v>0</v>
       </c>
       <c r="O195" s="1">
-        <v>349.55599317341427</v>
+        <f t="shared" ref="O195:O258" si="3">+SUM(C195:N195)</f>
+        <v>330.58684449548207</v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.35">
@@ -12140,7 +12334,7 @@
         <v>0</v>
       </c>
       <c r="F196" s="1">
-        <v>82.783801148456007</v>
+        <v>76.161097056579536</v>
       </c>
       <c r="G196" s="1">
         <v>0</v>
@@ -12167,7 +12361,8 @@
         <v>0</v>
       </c>
       <c r="O196" s="1">
-        <v>331.91278847065519</v>
+        <f t="shared" si="3"/>
+        <v>294.81402709392233</v>
       </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.35">
@@ -12187,7 +12382,7 @@
         <v>20.009742353779831</v>
       </c>
       <c r="F197" s="1">
-        <v>28.598040396739346</v>
+        <v>26.310197165000201</v>
       </c>
       <c r="G197" s="1">
         <v>30.446658404042331</v>
@@ -12214,7 +12409,8 @@
         <v>0</v>
       </c>
       <c r="O197" s="1">
-        <v>326.39928700104298</v>
+        <f t="shared" si="3"/>
+        <v>319.97703450968481</v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.35">
@@ -12261,7 +12457,8 @@
         <v>0</v>
       </c>
       <c r="O198" s="1">
-        <v>324.19388641319807</v>
+        <f t="shared" si="3"/>
+        <v>300.06372701289888</v>
       </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.35">
@@ -12308,7 +12505,8 @@
         <v>0</v>
       </c>
       <c r="O199" s="1">
-        <v>308.7560822982839</v>
+        <f t="shared" si="3"/>
+        <v>272.38772359221292</v>
       </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.35">
@@ -12355,7 +12553,8 @@
         <v>0</v>
       </c>
       <c r="O200" s="1">
-        <v>302.13988053474924</v>
+        <f t="shared" si="3"/>
+        <v>270.7344730927644</v>
       </c>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.35">
@@ -12402,7 +12601,8 @@
         <v>0</v>
       </c>
       <c r="O201" s="1">
-        <v>299.93447994690439</v>
+        <f t="shared" si="3"/>
+        <v>322.10920973279315</v>
       </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.35">
@@ -12449,7 +12649,8 @@
         <v>0</v>
       </c>
       <c r="O202" s="1">
-        <v>292.21557788944727</v>
+        <f t="shared" si="3"/>
+        <v>231.41410057024365</v>
       </c>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.35">
@@ -12481,7 +12682,7 @@
         <v>30.936993147924227</v>
       </c>
       <c r="J203" s="1">
-        <v>138.09178331018271</v>
+        <v>127.0444406453681</v>
       </c>
       <c r="K203" s="1">
         <v>19.464876513193254</v>
@@ -12496,7 +12697,8 @@
         <v>0</v>
       </c>
       <c r="O203" s="1">
-        <v>291.11287759552482</v>
+        <f t="shared" si="3"/>
+        <v>280.70136221937418</v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.35">
@@ -12543,7 +12745,8 @@
         <v>0</v>
       </c>
       <c r="O204" s="1">
-        <v>281.1885749502228</v>
+        <f t="shared" si="3"/>
+        <v>248.02637227156495</v>
       </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.35">
@@ -12590,7 +12793,8 @@
         <v>0</v>
       </c>
       <c r="O205" s="1">
-        <v>276.77777377453305</v>
+        <f t="shared" si="3"/>
+        <v>226.95284858113067</v>
       </c>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.35">
@@ -12637,7 +12841,8 @@
         <v>0</v>
       </c>
       <c r="O206" s="1">
-        <v>276.77777377453305</v>
+        <f t="shared" si="3"/>
+        <v>278.06863311551984</v>
       </c>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.35">
@@ -12684,7 +12889,8 @@
         <v>0</v>
       </c>
       <c r="O207" s="1">
-        <v>275.67507348061059</v>
+        <f t="shared" si="3"/>
+        <v>283.39044351353482</v>
       </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.35">
@@ -12731,7 +12937,8 @@
         <v>0</v>
       </c>
       <c r="O208" s="1">
-        <v>274.5723731866882</v>
+        <f t="shared" si="3"/>
+        <v>305.16938379983071</v>
       </c>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.35">
@@ -12778,7 +12985,8 @@
         <v>0</v>
       </c>
       <c r="O209" s="1">
-        <v>267.95617142315353</v>
+        <f t="shared" si="3"/>
+        <v>243.44887513051387</v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.35">
@@ -12825,7 +13033,8 @@
         <v>0</v>
       </c>
       <c r="O210" s="1">
-        <v>264.64807054138623</v>
+        <f t="shared" si="3"/>
+        <v>271.50647376698282</v>
       </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.35">
@@ -12872,7 +13081,8 @@
         <v>0</v>
       </c>
       <c r="O211" s="1">
-        <v>264.64807054138623</v>
+        <f t="shared" si="3"/>
+        <v>209.58258164852253</v>
       </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.35">
@@ -12919,7 +13129,8 @@
         <v>0</v>
       </c>
       <c r="O212" s="1">
-        <v>263.54537024746378</v>
+        <f t="shared" si="3"/>
+        <v>274.56625471603445</v>
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.35">
@@ -12966,7 +13177,8 @@
         <v>0</v>
       </c>
       <c r="O213" s="1">
-        <v>262.44266995354133</v>
+        <f t="shared" si="3"/>
+        <v>229.86224958980068</v>
       </c>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.35">
@@ -13013,7 +13225,8 @@
         <v>0</v>
       </c>
       <c r="O214" s="1">
-        <v>260.23726936569642</v>
+        <f t="shared" si="3"/>
+        <v>207.16176509535418</v>
       </c>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.35">
@@ -13060,7 +13273,8 @@
         <v>0</v>
       </c>
       <c r="O215" s="1">
-        <v>259.13456907177402</v>
+        <f t="shared" si="3"/>
+        <v>205.21627786417832</v>
       </c>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.35">
@@ -13107,7 +13321,8 @@
         <v>0</v>
       </c>
       <c r="O216" s="1">
-        <v>256.92916848392912</v>
+        <f t="shared" si="3"/>
+        <v>226.03603710354366</v>
       </c>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.35">
@@ -13154,7 +13369,8 @@
         <v>0</v>
       </c>
       <c r="O217" s="1">
-        <v>256.92916848392912</v>
+        <f t="shared" si="3"/>
+        <v>242.61703232938493</v>
       </c>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.35">
@@ -13201,7 +13417,8 @@
         <v>0</v>
       </c>
       <c r="O218" s="1">
-        <v>252.51836730823933</v>
+        <f t="shared" si="3"/>
+        <v>199.97671332296525</v>
       </c>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.35">
@@ -13248,7 +13465,8 @@
         <v>0</v>
       </c>
       <c r="O219" s="1">
-        <v>252.51836730823933</v>
+        <f t="shared" si="3"/>
+        <v>199.2177473831286</v>
       </c>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.35">
@@ -13295,7 +13513,8 @@
         <v>0</v>
       </c>
       <c r="O220" s="1">
-        <v>249.210266426472</v>
+        <f t="shared" si="3"/>
+        <v>202.97687671079552</v>
       </c>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.35">
@@ -13315,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="F221" s="1">
-        <v>12.041280167048146</v>
+        <v>11.077977753684294</v>
       </c>
       <c r="G221" s="1">
         <v>0</v>
@@ -13342,7 +13561,8 @@
         <v>0</v>
       </c>
       <c r="O221" s="1">
-        <v>248.10756613254955</v>
+        <f t="shared" si="3"/>
+        <v>200.57556199422345</v>
       </c>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.35">
@@ -13389,7 +13609,8 @@
         <v>0</v>
       </c>
       <c r="O222" s="1">
-        <v>247.00486583862713</v>
+        <f t="shared" si="3"/>
+        <v>243.10656117952337</v>
       </c>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.35">
@@ -13436,7 +13657,8 @@
         <v>0</v>
       </c>
       <c r="O223" s="1">
-        <v>247.00486583862713</v>
+        <f t="shared" si="3"/>
+        <v>302.09383992233791</v>
       </c>
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.35">
@@ -13456,7 +13678,7 @@
         <v>49.357364472656919</v>
       </c>
       <c r="F224" s="1">
-        <v>165.56760229691201</v>
+        <v>152.32219411315907</v>
       </c>
       <c r="G224" s="1">
         <v>68.200514825054825</v>
@@ -13483,7 +13705,8 @@
         <v>0</v>
       </c>
       <c r="O224" s="1">
-        <v>244.79946525078222</v>
+        <f t="shared" si="3"/>
+        <v>292.92378721227749</v>
       </c>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.35">
@@ -13530,7 +13753,8 @@
         <v>0</v>
       </c>
       <c r="O225" s="1">
-        <v>242.59406466293737</v>
+        <f t="shared" si="3"/>
+        <v>208.54610677355916</v>
       </c>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.35">
@@ -13550,7 +13774,7 @@
         <v>49.357364472656919</v>
       </c>
       <c r="F226" s="1">
-        <v>76.763161064931936</v>
+        <v>70.622108179737381</v>
       </c>
       <c r="G226" s="1">
         <v>0</v>
@@ -13577,7 +13801,8 @@
         <v>0</v>
       </c>
       <c r="O226" s="1">
-        <v>241.49136436901492</v>
+        <f t="shared" si="3"/>
+        <v>283.10513586323702</v>
       </c>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.35">
@@ -13624,7 +13849,8 @@
         <v>0</v>
       </c>
       <c r="O227" s="1">
-        <v>241.49136436901492</v>
+        <f t="shared" si="3"/>
+        <v>186.04834061041109</v>
       </c>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.35">
@@ -13644,7 +13870,7 @@
         <v>0</v>
       </c>
       <c r="F228" s="1">
-        <v>10.536120146167129</v>
+        <v>9.6932305344737593</v>
       </c>
       <c r="G228" s="1">
         <v>37.753856421012493</v>
@@ -13656,7 +13882,7 @@
         <v>78.156614268440151</v>
       </c>
       <c r="J228" s="1">
-        <v>22.825088150443424</v>
+        <v>20.999081098407949</v>
       </c>
       <c r="K228" s="1">
         <v>10.813820285107363</v>
@@ -13671,7 +13897,8 @@
         <v>0</v>
       </c>
       <c r="O228" s="1">
-        <v>237.08056319332516</v>
+        <f t="shared" si="3"/>
+        <v>214.12343288882414</v>
       </c>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.35">
@@ -13703,7 +13930,7 @@
         <v>69.201168883514711</v>
       </c>
       <c r="J229" s="1">
-        <v>89.017843786729344</v>
+        <v>81.896416283790998</v>
       </c>
       <c r="K229" s="1">
         <v>0</v>
@@ -13718,7 +13945,8 @@
         <v>0</v>
       </c>
       <c r="O229" s="1">
-        <v>235.97786289940268</v>
+        <f t="shared" si="3"/>
+        <v>208.07337956896168</v>
       </c>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.35">
@@ -13738,7 +13966,7 @@
         <v>70.70108965002207</v>
       </c>
       <c r="F230" s="1">
-        <v>57.196080793478693</v>
+        <v>52.620394330000401</v>
       </c>
       <c r="G230" s="1">
         <v>0</v>
@@ -13765,7 +13993,8 @@
         <v>0</v>
       </c>
       <c r="O230" s="1">
-        <v>222.74545937233336</v>
+        <f t="shared" si="3"/>
+        <v>236.32058659901037</v>
       </c>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.35">
@@ -13785,7 +14014,7 @@
         <v>0</v>
       </c>
       <c r="F231" s="1">
-        <v>180.6192025057222</v>
+        <v>166.16966630526443</v>
       </c>
       <c r="G231" s="1">
         <v>0</v>
@@ -13812,7 +14041,8 @@
         <v>0</v>
       </c>
       <c r="O231" s="1">
-        <v>217.23195790272115</v>
+        <f t="shared" si="3"/>
+        <v>244.47425776903816</v>
       </c>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.35">
@@ -13859,7 +14089,8 @@
         <v>0</v>
       </c>
       <c r="O232" s="1">
-        <v>216.12925760879872</v>
+        <f t="shared" si="3"/>
+        <v>192.36892535335909</v>
       </c>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.35">
@@ -13906,7 +14137,8 @@
         <v>0</v>
       </c>
       <c r="O233" s="1">
-        <v>213.92385702095388</v>
+        <f t="shared" si="3"/>
+        <v>289.29830874293901</v>
       </c>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.35">
@@ -13953,7 +14185,8 @@
         <v>0</v>
       </c>
       <c r="O234" s="1">
-        <v>212.82115672703139</v>
+        <f t="shared" si="3"/>
+        <v>184.70722873626551</v>
       </c>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.35">
@@ -13973,7 +14206,7 @@
         <v>0</v>
       </c>
       <c r="F235" s="1">
-        <v>19.567080271453239</v>
+        <v>18.00171384973698</v>
       </c>
       <c r="G235" s="1">
         <v>0</v>
@@ -13985,7 +14218,7 @@
         <v>9.7695767835550189</v>
       </c>
       <c r="J235" s="1">
-        <v>21.683833742921252</v>
+        <v>19.94912704348755</v>
       </c>
       <c r="K235" s="1">
         <v>33.52284288383283</v>
@@ -14000,7 +14233,8 @@
         <v>0</v>
       </c>
       <c r="O235" s="1">
-        <v>211.71845643310897</v>
+        <f t="shared" si="3"/>
+        <v>196.07023181522396</v>
       </c>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.35">
@@ -14047,7 +14281,8 @@
         <v>0</v>
       </c>
       <c r="O236" s="1">
-        <v>211.71845643310897</v>
+        <f t="shared" si="3"/>
+        <v>193.4288907676364</v>
       </c>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.35">
@@ -14094,7 +14329,8 @@
         <v>0</v>
       </c>
       <c r="O237" s="1">
-        <v>210.61575613918652</v>
+        <f t="shared" si="3"/>
+        <v>217.80556920203281</v>
       </c>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.35">
@@ -14141,7 +14377,8 @@
         <v>0</v>
       </c>
       <c r="O238" s="1">
-        <v>205.10225466957434</v>
+        <f t="shared" si="3"/>
+        <v>151.4284401451028</v>
       </c>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.35">
@@ -14188,7 +14425,8 @@
         <v>0</v>
       </c>
       <c r="O239" s="1">
-        <v>201.79415378780698</v>
+        <f t="shared" si="3"/>
+        <v>227.51031641456197</v>
       </c>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.35">
@@ -14208,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="F240" s="1">
-        <v>30.103200417620368</v>
+        <v>27.694944384210736</v>
       </c>
       <c r="G240" s="1">
         <v>53.586118791114501</v>
@@ -14235,7 +14473,8 @@
         <v>0</v>
       </c>
       <c r="O240" s="1">
-        <v>200.69145349388452</v>
+        <f t="shared" si="3"/>
+        <v>201.9152227368356</v>
       </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.35">
@@ -14255,7 +14494,7 @@
         <v>0</v>
       </c>
       <c r="F241" s="1">
-        <v>91.814761273742121</v>
+        <v>84.469580371842753</v>
       </c>
       <c r="G241" s="1">
         <v>0</v>
@@ -14282,7 +14521,8 @@
         <v>0</v>
       </c>
       <c r="O241" s="1">
-        <v>197.38335261211722</v>
+        <f t="shared" si="3"/>
+        <v>188.01760767853062</v>
       </c>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.35">
@@ -14302,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="F242" s="1">
-        <v>267.9184837168213</v>
+        <v>246.48500501947558</v>
       </c>
       <c r="G242" s="1">
         <v>0</v>
@@ -14329,7 +14569,8 @@
         <v>0</v>
       </c>
       <c r="O242" s="1">
-        <v>196.28065231819477</v>
+        <f t="shared" si="3"/>
+        <v>246.48500501947558</v>
       </c>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.35">
@@ -14349,7 +14590,7 @@
         <v>0</v>
       </c>
       <c r="F243" s="1">
-        <v>43.649640605549536</v>
+        <v>40.157669357105569</v>
       </c>
       <c r="G243" s="1">
         <v>0</v>
@@ -14361,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="1">
-        <v>49.073939523453362</v>
+        <v>45.148024361577093</v>
       </c>
       <c r="K243" s="1">
         <v>28.115932741279149</v>
@@ -14376,7 +14617,8 @@
         <v>0</v>
       </c>
       <c r="O243" s="1">
-        <v>195.17795202427234</v>
+        <f t="shared" si="3"/>
+        <v>222.95814917564968</v>
       </c>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.35">
@@ -14408,7 +14650,7 @@
         <v>39.89243853284966</v>
       </c>
       <c r="J244" s="1">
-        <v>49.073939523453362</v>
+        <v>45.148024361577093</v>
       </c>
       <c r="K244" s="1">
         <v>21.627640570214727</v>
@@ -14423,7 +14665,8 @@
         <v>0</v>
       </c>
       <c r="O244" s="1">
-        <v>195.17795202427234</v>
+        <f t="shared" si="3"/>
+        <v>195.10754347619934</v>
       </c>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.35">
@@ -14470,7 +14713,8 @@
         <v>0</v>
       </c>
       <c r="O245" s="1">
-        <v>194.07525173034986</v>
+        <f t="shared" si="3"/>
+        <v>143.28712615880693</v>
       </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.35">
@@ -14490,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="F246" s="1">
-        <v>27.092880375858332</v>
+        <v>24.925449945789666</v>
       </c>
       <c r="G246" s="1">
         <v>21.921594050910478</v>
@@ -14517,7 +14761,8 @@
         <v>0</v>
       </c>
       <c r="O246" s="1">
-        <v>192.97255143642744</v>
+        <f t="shared" si="3"/>
+        <v>202.64077403478552</v>
       </c>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.35">
@@ -14564,7 +14809,8 @@
         <v>0</v>
       </c>
       <c r="O247" s="1">
-        <v>192.97255143642744</v>
+        <f t="shared" si="3"/>
+        <v>260.964969226878</v>
       </c>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.35">
@@ -14611,7 +14857,8 @@
         <v>0</v>
       </c>
       <c r="O248" s="1">
-        <v>192.97255143642744</v>
+        <f t="shared" si="3"/>
+        <v>159.61740070991431</v>
       </c>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.35">
@@ -14658,7 +14905,8 @@
         <v>0</v>
       </c>
       <c r="O249" s="1">
-        <v>191.86985114250498</v>
+        <f t="shared" si="3"/>
+        <v>158.38073054102097</v>
       </c>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.35">
@@ -14705,7 +14953,8 @@
         <v>0</v>
       </c>
       <c r="O250" s="1">
-        <v>190.76715084858256</v>
+        <f t="shared" si="3"/>
+        <v>210.69087615597294</v>
       </c>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.35">
@@ -14752,7 +15001,8 @@
         <v>0</v>
       </c>
       <c r="O251" s="1">
-        <v>190.76715084858256</v>
+        <f t="shared" si="3"/>
+        <v>210.69087615597294</v>
       </c>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.35">
@@ -14799,7 +15049,8 @@
         <v>0</v>
       </c>
       <c r="O252" s="1">
-        <v>188.56175026073768</v>
+        <f t="shared" si="3"/>
+        <v>153.46860201499942</v>
       </c>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.35">
@@ -14846,7 +15097,8 @@
         <v>0</v>
       </c>
       <c r="O253" s="1">
-        <v>186.35634967289278</v>
+        <f t="shared" si="3"/>
+        <v>173.28306960425678</v>
       </c>
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.35">
@@ -14893,7 +15145,8 @@
         <v>0</v>
       </c>
       <c r="O254" s="1">
-        <v>183.04824879112545</v>
+        <f t="shared" si="3"/>
+        <v>198.11398196243323</v>
       </c>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.35">
@@ -14940,7 +15193,8 @@
         <v>0</v>
       </c>
       <c r="O255" s="1">
-        <v>179.74014790935814</v>
+        <f t="shared" si="3"/>
+        <v>194.30999661856339</v>
       </c>
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.35">
@@ -14987,7 +15241,8 @@
         <v>0</v>
       </c>
       <c r="O256" s="1">
-        <v>174.22664643974591</v>
+        <f t="shared" si="3"/>
+        <v>228.34173223818055</v>
       </c>
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.35">
@@ -15034,7 +15289,8 @@
         <v>0</v>
       </c>
       <c r="O257" s="1">
-        <v>169.81584526405612</v>
+        <f t="shared" si="3"/>
+        <v>174.46932372423322</v>
       </c>
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.35">
@@ -15081,7 +15337,8 @@
         <v>0</v>
       </c>
       <c r="O258" s="1">
-        <v>166.50774438228882</v>
+        <f t="shared" si="3"/>
+        <v>147.04644359388087</v>
       </c>
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.35">
@@ -15113,7 +15370,7 @@
         <v>0</v>
       </c>
       <c r="J259" s="1">
-        <v>116.40794956726145</v>
+        <v>107.09531360188053</v>
       </c>
       <c r="K259" s="1">
         <v>0</v>
@@ -15128,7 +15385,8 @@
         <v>0</v>
       </c>
       <c r="O259" s="1">
-        <v>164.30234379444394</v>
+        <f t="shared" ref="O259:O322" si="4">+SUM(C259:N259)</f>
+        <v>177.18304819424205</v>
       </c>
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.35">
@@ -15175,7 +15433,8 @@
         <v>0</v>
       </c>
       <c r="O260" s="1">
-        <v>163.19964350052149</v>
+        <f t="shared" si="4"/>
+        <v>129.2425920165889</v>
       </c>
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.35">
@@ -15195,7 +15454,7 @@
         <v>37.351519060389016</v>
       </c>
       <c r="F261" s="1">
-        <v>307.05264425972774</v>
+        <v>282.48843271894953</v>
       </c>
       <c r="G261" s="1">
         <v>0</v>
@@ -15222,7 +15481,8 @@
         <v>0</v>
       </c>
       <c r="O261" s="1">
-        <v>163.19964350052149</v>
+        <f t="shared" si="4"/>
+        <v>76.512435292934668</v>
       </c>
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.35">
@@ -15242,7 +15502,7 @@
         <v>0</v>
       </c>
       <c r="F262" s="1">
-        <v>45.15480062643055</v>
+        <v>41.542416576316107</v>
       </c>
       <c r="G262" s="1">
         <v>42.625321765659265</v>
@@ -15269,7 +15529,8 @@
         <v>0</v>
       </c>
       <c r="O262" s="1">
-        <v>159.89154261875416</v>
+        <f t="shared" si="4"/>
+        <v>173.37886172578251</v>
       </c>
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.35">
@@ -15316,7 +15577,8 @@
         <v>0</v>
       </c>
       <c r="O263" s="1">
-        <v>156.58344173698686</v>
+        <f t="shared" si="4"/>
+        <v>157.61262238609069</v>
       </c>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.35">
@@ -15336,7 +15598,7 @@
         <v>0</v>
       </c>
       <c r="F264" s="1">
-        <v>18.061920250572221</v>
+        <v>16.616966630526441</v>
       </c>
       <c r="G264" s="1">
         <v>4.8714653446467731</v>
@@ -15363,7 +15625,8 @@
         <v>0</v>
       </c>
       <c r="O264" s="1">
-        <v>153.2753408552195</v>
+        <f t="shared" si="4"/>
+        <v>156.2559531251726</v>
       </c>
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.35">
@@ -15383,7 +15646,7 @@
         <v>66.699141179266107</v>
       </c>
       <c r="F265" s="1">
-        <v>27.092880375858332</v>
+        <v>24.925449945789666</v>
       </c>
       <c r="G265" s="1">
         <v>0</v>
@@ -15410,7 +15673,8 @@
         <v>0</v>
       </c>
       <c r="O265" s="1">
-        <v>151.06994026737462</v>
+        <f t="shared" si="4"/>
+        <v>161.76544733557483</v>
       </c>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.35">
@@ -15457,7 +15721,8 @@
         <v>0</v>
       </c>
       <c r="O266" s="1">
-        <v>146.65913909168486</v>
+        <f t="shared" si="4"/>
+        <v>121.06113311468845</v>
       </c>
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.35">
@@ -15504,7 +15769,8 @@
         <v>0</v>
       </c>
       <c r="O267" s="1">
-        <v>141.14563762207266</v>
+        <f t="shared" si="4"/>
+        <v>168.49320187870174</v>
       </c>
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.35">
@@ -15551,7 +15817,8 @@
         <v>0</v>
       </c>
       <c r="O268" s="1">
-        <v>137.8375367403053</v>
+        <f t="shared" si="4"/>
+        <v>109.15759460860549</v>
       </c>
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.35">
@@ -15598,7 +15865,8 @@
         <v>0</v>
       </c>
       <c r="O269" s="1">
-        <v>137.8375367403053</v>
+        <f t="shared" si="4"/>
+        <v>111.15415425041857</v>
       </c>
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.35">
@@ -15618,7 +15886,7 @@
         <v>13.33982823585322</v>
       </c>
       <c r="F270" s="1">
-        <v>13.546440187929166</v>
+        <v>12.462724972894833</v>
       </c>
       <c r="G270" s="1">
         <v>48.714653446467729</v>
@@ -15630,7 +15898,7 @@
         <v>7.3271825876662646</v>
       </c>
       <c r="J270" s="1">
-        <v>11.412544075221712</v>
+        <v>10.499540549203974</v>
       </c>
       <c r="K270" s="1">
         <v>0</v>
@@ -15645,7 +15913,8 @@
         <v>0</v>
       </c>
       <c r="O270" s="1">
-        <v>136.73483644638287</v>
+        <f t="shared" si="4"/>
+        <v>145.51248525359605</v>
       </c>
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.35">
@@ -15677,7 +15946,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="1">
-        <v>116.40794956726145</v>
+        <v>107.09531360188053</v>
       </c>
       <c r="K271" s="1">
         <v>0</v>
@@ -15692,7 +15961,8 @@
         <v>0</v>
       </c>
       <c r="O271" s="1">
-        <v>134.52943585853799</v>
+        <f t="shared" si="4"/>
+        <v>127.54178132417043</v>
       </c>
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.35">
@@ -15739,7 +16009,8 @@
         <v>0</v>
       </c>
       <c r="O272" s="1">
-        <v>125.70783350715845</v>
+        <f t="shared" si="4"/>
+        <v>118.67541381363213</v>
       </c>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.35">
@@ -15759,7 +16030,7 @@
         <v>0</v>
       </c>
       <c r="F273" s="1">
-        <v>46.659960647311571</v>
+        <v>42.927163795526646</v>
       </c>
       <c r="G273" s="1">
         <v>0</v>
@@ -15786,7 +16057,8 @@
         <v>0</v>
       </c>
       <c r="O273" s="1">
-        <v>125.70783350715845</v>
+        <f t="shared" si="4"/>
+        <v>154.03868537321895</v>
       </c>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.35">
@@ -15833,7 +16105,8 @@
         <v>0</v>
       </c>
       <c r="O274" s="1">
-        <v>124.605133213236</v>
+        <f t="shared" si="4"/>
+        <v>98.678465526179366</v>
       </c>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.35">
@@ -15880,7 +16153,8 @@
         <v>0</v>
       </c>
       <c r="O275" s="1">
-        <v>123.50243291931356</v>
+        <f t="shared" si="4"/>
+        <v>95.458726724611935</v>
       </c>
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.35">
@@ -15927,7 +16201,8 @@
         <v>0</v>
       </c>
       <c r="O276" s="1">
-        <v>123.50243291931356</v>
+        <f t="shared" si="4"/>
+        <v>107.62700143115885</v>
       </c>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.35">
@@ -15974,7 +16249,8 @@
         <v>0</v>
       </c>
       <c r="O277" s="1">
-        <v>123.50243291931356</v>
+        <f t="shared" si="4"/>
+        <v>101.94621735973764</v>
       </c>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.35">
@@ -15994,7 +16270,7 @@
         <v>0</v>
       </c>
       <c r="F278" s="1">
-        <v>15.051600208810184</v>
+        <v>13.847472192105368</v>
       </c>
       <c r="G278" s="1">
         <v>29.228792067880637</v>
@@ -16021,7 +16297,8 @@
         <v>0</v>
       </c>
       <c r="O278" s="1">
-        <v>119.09163174362379</v>
+        <f t="shared" si="4"/>
+        <v>112.78746179755196</v>
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.35">
@@ -16041,7 +16318,7 @@
         <v>38.685501883974339</v>
       </c>
       <c r="F279" s="1">
-        <v>87.299281211099071</v>
+        <v>80.315338714211137</v>
       </c>
       <c r="G279" s="1">
         <v>0</v>
@@ -16068,7 +16345,8 @@
         <v>0</v>
       </c>
       <c r="O279" s="1">
-        <v>119.09163174362379</v>
+        <f t="shared" si="4"/>
+        <v>147.32213809090464</v>
       </c>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.35">
@@ -16115,7 +16393,8 @@
         <v>0</v>
       </c>
       <c r="O280" s="1">
-        <v>117.98893144970134</v>
+        <f t="shared" si="4"/>
+        <v>113.92124780252541</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.35">
@@ -16162,7 +16441,8 @@
         <v>0</v>
       </c>
       <c r="O281" s="1">
-        <v>116.8862311557789</v>
+        <f t="shared" si="4"/>
+        <v>137.72444556644228</v>
       </c>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.35">
@@ -16209,7 +16489,8 @@
         <v>0</v>
       </c>
       <c r="O282" s="1">
-        <v>113.57813027401157</v>
+        <f t="shared" si="4"/>
+        <v>95.614561773617908</v>
       </c>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.35">
@@ -16256,7 +16537,8 @@
         <v>0</v>
       </c>
       <c r="O283" s="1">
-        <v>108.06462880439936</v>
+        <f t="shared" si="4"/>
+        <v>105.97543879405217</v>
       </c>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.35">
@@ -16303,7 +16585,8 @@
         <v>0</v>
       </c>
       <c r="O284" s="1">
-        <v>106.96192851047694</v>
+        <f t="shared" si="4"/>
+        <v>78.970745667069735</v>
       </c>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.35">
@@ -16350,7 +16633,8 @@
         <v>0</v>
       </c>
       <c r="O285" s="1">
-        <v>105.85922821655448</v>
+        <f t="shared" si="4"/>
+        <v>111.80516547469699</v>
       </c>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.35">
@@ -16397,7 +16681,8 @@
         <v>0</v>
       </c>
       <c r="O286" s="1">
-        <v>105.85922821655448</v>
+        <f t="shared" si="4"/>
+        <v>78.156614268440151</v>
       </c>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.35">
@@ -16444,7 +16729,8 @@
         <v>0</v>
       </c>
       <c r="O287" s="1">
-        <v>105.85922821655448</v>
+        <f t="shared" si="4"/>
+        <v>78.156614268440151</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.35">
@@ -16491,7 +16777,8 @@
         <v>0</v>
       </c>
       <c r="O288" s="1">
-        <v>105.85922821655448</v>
+        <f t="shared" si="4"/>
+        <v>93.714330655754551</v>
       </c>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.35">
@@ -16538,7 +16825,8 @@
         <v>0</v>
       </c>
       <c r="O289" s="1">
-        <v>104.75652792263205</v>
+        <f t="shared" si="4"/>
+        <v>82.959771902540169</v>
       </c>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.35">
@@ -16585,7 +16873,8 @@
         <v>0</v>
       </c>
       <c r="O290" s="1">
-        <v>103.65382762870959</v>
+        <f t="shared" si="4"/>
+        <v>96.09839829476249</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.35">
@@ -16632,7 +16921,8 @@
         <v>0</v>
       </c>
       <c r="O291" s="1">
-        <v>103.65382762870959</v>
+        <f t="shared" si="4"/>
+        <v>82.086511145671338</v>
       </c>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.35">
@@ -16679,7 +16969,8 @@
         <v>0</v>
       </c>
       <c r="O292" s="1">
-        <v>101.44842704086471</v>
+        <f t="shared" si="4"/>
+        <v>122.72641976984963</v>
       </c>
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.35">
@@ -16726,7 +17017,8 @@
         <v>0</v>
       </c>
       <c r="O293" s="1">
-        <v>100.34572674694226</v>
+        <f t="shared" si="4"/>
+        <v>74.085957275292216</v>
       </c>
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.35">
@@ -16773,7 +17065,8 @@
         <v>0</v>
       </c>
       <c r="O294" s="1">
-        <v>98.140326159097384</v>
+        <f t="shared" si="4"/>
+        <v>132.71932720681224</v>
       </c>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.35">
@@ -16793,7 +17086,7 @@
         <v>0</v>
       </c>
       <c r="F295" s="1">
-        <v>97.835401357266193</v>
+        <v>90.008569248684893</v>
       </c>
       <c r="G295" s="1">
         <v>0</v>
@@ -16820,7 +17113,8 @@
         <v>0</v>
       </c>
       <c r="O295" s="1">
-        <v>94.832225277330053</v>
+        <f t="shared" si="4"/>
+        <v>112.71759184741035</v>
       </c>
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.35">
@@ -16867,7 +17161,8 @@
         <v>0</v>
       </c>
       <c r="O296" s="1">
-        <v>94.832225277330053</v>
+        <f t="shared" si="4"/>
+        <v>70.01530028214431</v>
       </c>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.35">
@@ -16899,7 +17194,7 @@
         <v>0</v>
       </c>
       <c r="J297" s="1">
-        <v>94.724115824340217</v>
+        <v>87.146186558392998</v>
       </c>
       <c r="K297" s="1">
         <v>0</v>
@@ -16914,7 +17209,8 @@
         <v>0</v>
       </c>
       <c r="O297" s="1">
-        <v>91.524124395562723</v>
+        <f t="shared" si="4"/>
+        <v>87.146186558392998</v>
       </c>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.35">
@@ -16934,7 +17230,7 @@
         <v>0</v>
       </c>
       <c r="F298" s="1">
-        <v>49.670280689073607</v>
+        <v>45.696658233947716</v>
       </c>
       <c r="G298" s="1">
         <v>0</v>
@@ -16961,7 +17257,8 @@
         <v>0</v>
       </c>
       <c r="O298" s="1">
-        <v>89.318723807717845</v>
+        <f t="shared" si="4"/>
+        <v>87.613174563652223</v>
       </c>
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.35">
@@ -16981,7 +17278,7 @@
         <v>0</v>
       </c>
       <c r="F299" s="1">
-        <v>115.89732160783841</v>
+        <v>106.62553587921134</v>
       </c>
       <c r="G299" s="1">
         <v>0</v>
@@ -17008,7 +17305,8 @@
         <v>0</v>
       </c>
       <c r="O299" s="1">
-        <v>84.907922632028061</v>
+        <f t="shared" si="4"/>
+        <v>106.62553587921134</v>
       </c>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.35">
@@ -17055,7 +17353,8 @@
         <v>0</v>
       </c>
       <c r="O300" s="1">
-        <v>84.907922632028061</v>
+        <f t="shared" si="4"/>
+        <v>68.904877980411882</v>
       </c>
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.35">
@@ -17102,7 +17401,8 @@
         <v>0</v>
       </c>
       <c r="O301" s="1">
-        <v>82.702522044183183</v>
+        <f t="shared" si="4"/>
+        <v>68.267556267681456</v>
       </c>
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.35">
@@ -17149,7 +17449,8 @@
         <v>0</v>
       </c>
       <c r="O302" s="1">
-        <v>79.394421162415867</v>
+        <f t="shared" si="4"/>
+        <v>65.904180263301953</v>
       </c>
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.35">
@@ -17196,7 +17497,8 @@
         <v>0</v>
       </c>
       <c r="O303" s="1">
-        <v>77.189020574570975</v>
+        <f t="shared" si="4"/>
+        <v>56.989197904070949</v>
       </c>
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.35">
@@ -17243,7 +17545,8 @@
         <v>0</v>
       </c>
       <c r="O304" s="1">
-        <v>77.189020574570975</v>
+        <f t="shared" si="4"/>
+        <v>104.38598769075121</v>
       </c>
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.35">
@@ -17263,7 +17566,7 @@
         <v>0</v>
       </c>
       <c r="F305" s="1">
-        <v>52.680600730835643</v>
+        <v>48.466152672368793</v>
       </c>
       <c r="G305" s="1">
         <v>0</v>
@@ -17290,7 +17593,8 @@
         <v>0</v>
       </c>
       <c r="O305" s="1">
-        <v>76.086320280648536</v>
+        <f t="shared" si="4"/>
+        <v>91.196532961211915</v>
       </c>
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.35">
@@ -17337,7 +17641,8 @@
         <v>0</v>
       </c>
       <c r="O306" s="1">
-        <v>73.880919692803658</v>
+        <f t="shared" si="4"/>
+        <v>64.769101138529862</v>
       </c>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.35">
@@ -17357,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="F307" s="1">
-        <v>33.113520459382407</v>
+        <v>30.464438822631813</v>
       </c>
       <c r="G307" s="1">
         <v>0</v>
@@ -17384,7 +17689,8 @@
         <v>0</v>
       </c>
       <c r="O307" s="1">
-        <v>71.675519104958767</v>
+        <f t="shared" si="4"/>
+        <v>68.014651367992101</v>
       </c>
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.35">
@@ -17404,7 +17710,7 @@
         <v>0</v>
       </c>
       <c r="F308" s="1">
-        <v>22.577400313215275</v>
+        <v>20.771208288158054</v>
       </c>
       <c r="G308" s="1">
         <v>60.893316808084663</v>
@@ -17431,7 +17737,8 @@
         <v>0</v>
       </c>
       <c r="O308" s="1">
-        <v>71.675519104958767</v>
+        <f t="shared" si="4"/>
+        <v>81.664525096242713</v>
       </c>
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.35">
@@ -17451,7 +17758,7 @@
         <v>0</v>
       </c>
       <c r="F309" s="1">
-        <v>13.546440187929166</v>
+        <v>12.462724972894833</v>
       </c>
       <c r="G309" s="1">
         <v>36.535990084850802</v>
@@ -17478,7 +17785,8 @@
         <v>0</v>
       </c>
       <c r="O309" s="1">
-        <v>71.675519104958767</v>
+        <f t="shared" si="4"/>
+        <v>71.703494736335585</v>
       </c>
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.35">
@@ -17525,7 +17833,8 @@
         <v>0</v>
       </c>
       <c r="O310" s="1">
-        <v>70.572818811036328</v>
+        <f t="shared" si="4"/>
+        <v>65.428696711327646</v>
       </c>
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.35">
@@ -17572,7 +17881,8 @@
         <v>0</v>
       </c>
       <c r="O311" s="1">
-        <v>69.470118517113875</v>
+        <f t="shared" si="4"/>
+        <v>57.344747264852423</v>
       </c>
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.35">
@@ -17619,7 +17929,8 @@
         <v>0</v>
       </c>
       <c r="O312" s="1">
-        <v>69.470118517113875</v>
+        <f t="shared" si="4"/>
+        <v>64.839088948802583</v>
       </c>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.35">
@@ -17666,7 +17977,8 @@
         <v>0</v>
       </c>
       <c r="O313" s="1">
-        <v>68.367418223191436</v>
+        <f t="shared" si="4"/>
+        <v>77.912957353803989</v>
       </c>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.35">
@@ -17713,7 +18025,8 @@
         <v>0</v>
       </c>
       <c r="O314" s="1">
-        <v>68.367418223191436</v>
+        <f t="shared" si="4"/>
+        <v>64.919574641400956</v>
       </c>
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.35">
@@ -17760,7 +18073,8 @@
         <v>0</v>
       </c>
       <c r="O315" s="1">
-        <v>67.264717929268997</v>
+        <f t="shared" si="4"/>
+        <v>53.670774764621953</v>
       </c>
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.35">
@@ -17807,7 +18121,8 @@
         <v>0</v>
       </c>
       <c r="O316" s="1">
-        <v>67.264717929268997</v>
+        <f t="shared" si="4"/>
+        <v>81.372952238704656</v>
       </c>
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.35">
@@ -17854,7 +18169,8 @@
         <v>0</v>
       </c>
       <c r="O317" s="1">
-        <v>63.956617047501666</v>
+        <f t="shared" si="4"/>
+        <v>79.789273406537149</v>
       </c>
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.35">
@@ -17886,7 +18202,7 @@
         <v>0</v>
       </c>
       <c r="J318" s="1">
-        <v>23.966342557965593</v>
+        <v>22.049035153328347</v>
       </c>
       <c r="K318" s="1">
         <v>9.7324382565966268</v>
@@ -17901,7 +18217,8 @@
         <v>0</v>
       </c>
       <c r="O318" s="1">
-        <v>62.853916753579227</v>
+        <f t="shared" si="4"/>
+        <v>57.366597389198972</v>
       </c>
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.35">
@@ -17921,7 +18238,7 @@
         <v>0</v>
       </c>
       <c r="F319" s="1">
-        <v>85.79412119021805</v>
+        <v>78.930591495000613</v>
       </c>
       <c r="G319" s="1">
         <v>0</v>
@@ -17948,7 +18265,8 @@
         <v>0</v>
       </c>
       <c r="O319" s="1">
-        <v>62.853916753579227</v>
+        <f t="shared" si="4"/>
+        <v>78.930591495000613</v>
       </c>
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.35">
@@ -17980,7 +18298,7 @@
         <v>21.167416364369206</v>
       </c>
       <c r="J320" s="1">
-        <v>34.237632225665138</v>
+        <v>31.498621647611927</v>
       </c>
       <c r="K320" s="1">
         <v>0</v>
@@ -17995,7 +18313,8 @@
         <v>0</v>
       </c>
       <c r="O320" s="1">
-        <v>61.751216459656781</v>
+        <f t="shared" si="4"/>
+        <v>52.666038011981129</v>
       </c>
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.35">
@@ -18042,7 +18361,8 @@
         <v>0</v>
       </c>
       <c r="O321" s="1">
-        <v>61.751216459656781</v>
+        <f t="shared" si="4"/>
+        <v>63.171638934357418</v>
       </c>
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.35">
@@ -18074,7 +18394,7 @@
         <v>131.07515517936318</v>
       </c>
       <c r="J322" s="1">
-        <v>-190.58948605620259</v>
+        <v>-175.34232717170639</v>
       </c>
       <c r="K322" s="1">
         <v>0</v>
@@ -18089,7 +18409,8 @@
         <v>0</v>
       </c>
       <c r="O322" s="1">
-        <v>60.648516165734343</v>
+        <f t="shared" si="4"/>
+        <v>25.164397717041851</v>
       </c>
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.35">
@@ -18136,7 +18457,8 @@
         <v>0</v>
       </c>
       <c r="O323" s="1">
-        <v>59.545815871811897</v>
+        <f t="shared" ref="O323:O386" si="5">+SUM(C323:N323)</f>
+        <v>80.526333361436642</v>
       </c>
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.35">
@@ -18156,7 +18478,7 @@
         <v>0</v>
       </c>
       <c r="F324" s="1">
-        <v>40.639320563787493</v>
+        <v>37.388174918684498</v>
       </c>
       <c r="G324" s="1">
         <v>0</v>
@@ -18183,7 +18505,8 @@
         <v>0</v>
       </c>
       <c r="O324" s="1">
-        <v>59.545815871811897</v>
+        <f t="shared" si="5"/>
+        <v>64.990906343775848</v>
       </c>
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.35">
@@ -18230,7 +18553,8 @@
         <v>0</v>
       </c>
       <c r="O325" s="1">
-        <v>59.545815871811897</v>
+        <f t="shared" si="5"/>
+        <v>61.353521065005197</v>
       </c>
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.35">
@@ -18277,7 +18601,8 @@
         <v>0</v>
       </c>
       <c r="O326" s="1">
-        <v>58.443115577889451</v>
+        <f t="shared" si="5"/>
+        <v>47.272195140019292</v>
       </c>
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.35">
@@ -18324,7 +18649,8 @@
         <v>0</v>
       </c>
       <c r="O327" s="1">
-        <v>56.237714990044566</v>
+        <f t="shared" si="5"/>
+        <v>45.978258341620482</v>
       </c>
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.35">
@@ -18371,7 +18697,8 @@
         <v>0</v>
       </c>
       <c r="O328" s="1">
-        <v>55.135014696122127</v>
+        <f t="shared" si="5"/>
+        <v>74.561419779108007</v>
       </c>
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.35">
@@ -18418,7 +18745,8 @@
         <v>0</v>
       </c>
       <c r="O329" s="1">
-        <v>50.724213520432357</v>
+        <f t="shared" si="5"/>
+        <v>61.363209884924814</v>
       </c>
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.35">
@@ -18450,7 +18778,7 @@
         <v>0</v>
       </c>
       <c r="J330" s="1">
-        <v>51.356448338497707</v>
+        <v>47.24793247141789</v>
       </c>
       <c r="K330" s="1">
         <v>0</v>
@@ -18465,7 +18793,8 @@
         <v>0</v>
       </c>
       <c r="O330" s="1">
-        <v>49.621513226509911</v>
+        <f t="shared" si="5"/>
+        <v>47.24793247141789</v>
       </c>
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.35">
@@ -18485,7 +18814,7 @@
         <v>0</v>
       </c>
       <c r="F331" s="1">
-        <v>18.061920250572221</v>
+        <v>16.616966630526441</v>
       </c>
       <c r="G331" s="1">
         <v>0</v>
@@ -18512,7 +18841,8 @@
         <v>0</v>
       </c>
       <c r="O331" s="1">
-        <v>48.518812932587466</v>
+        <f t="shared" si="5"/>
+        <v>45.744457304737196</v>
       </c>
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.35">
@@ -18559,7 +18889,8 @@
         <v>0</v>
       </c>
       <c r="O332" s="1">
-        <v>47.416112638665027</v>
+        <f t="shared" si="5"/>
+        <v>46.499427225961668</v>
       </c>
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.35">
@@ -18606,7 +18937,8 @@
         <v>0</v>
       </c>
       <c r="O333" s="1">
-        <v>47.416112638665027</v>
+        <f t="shared" si="5"/>
+        <v>35.598943723464743</v>
       </c>
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.35">
@@ -18653,7 +18985,8 @@
         <v>0</v>
       </c>
       <c r="O334" s="1">
-        <v>46.313412344742581</v>
+        <f t="shared" si="5"/>
+        <v>39.39203299199994</v>
       </c>
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.35">
@@ -18700,7 +19033,8 @@
         <v>0</v>
       </c>
       <c r="O335" s="1">
-        <v>44.108011756897696</v>
+        <f t="shared" si="5"/>
+        <v>37.321881401428563</v>
       </c>
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.35">
@@ -18747,7 +19081,8 @@
         <v>0</v>
       </c>
       <c r="O336" s="1">
-        <v>43.005311462975257</v>
+        <f t="shared" si="5"/>
+        <v>52.025330119827565</v>
       </c>
     </row>
     <row r="337" spans="1:15" x14ac:dyDescent="0.35">
@@ -18794,7 +19129,8 @@
         <v>0</v>
       </c>
       <c r="O337" s="1">
-        <v>43.005311462975257</v>
+        <f t="shared" si="5"/>
+        <v>43.394342733135687</v>
       </c>
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.35">
@@ -18841,7 +19177,8 @@
         <v>0</v>
       </c>
       <c r="O338" s="1">
-        <v>43.005311462975257</v>
+        <f t="shared" si="5"/>
+        <v>35.499129259194355</v>
       </c>
     </row>
     <row r="339" spans="1:15" x14ac:dyDescent="0.35">
@@ -18888,7 +19225,8 @@
         <v>0</v>
       </c>
       <c r="O339" s="1">
-        <v>41.902611169052811</v>
+        <f t="shared" si="5"/>
+        <v>51.248062129682317</v>
       </c>
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.35">
@@ -18935,7 +19273,8 @@
         <v>0</v>
       </c>
       <c r="O340" s="1">
-        <v>40.799910875130372</v>
+        <f t="shared" si="5"/>
+        <v>49.357364472656919</v>
       </c>
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.35">
@@ -18982,7 +19321,8 @@
         <v>0</v>
       </c>
       <c r="O341" s="1">
-        <v>40.799910875130372</v>
+        <f t="shared" si="5"/>
+        <v>40.011135054897245</v>
       </c>
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.35">
@@ -19002,7 +19342,7 @@
         <v>0</v>
       </c>
       <c r="F342" s="1">
-        <v>33.113520459382407</v>
+        <v>30.464438822631813</v>
       </c>
       <c r="G342" s="1">
         <v>0</v>
@@ -19029,7 +19369,8 @@
         <v>0</v>
       </c>
       <c r="O342" s="1">
-        <v>39.697210581207933</v>
+        <f t="shared" si="5"/>
+        <v>42.69008941879563</v>
       </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.35">
@@ -19076,7 +19417,8 @@
         <v>0</v>
       </c>
       <c r="O343" s="1">
-        <v>38.594510287285487</v>
+        <f t="shared" si="5"/>
+        <v>37.412867653129879</v>
       </c>
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.35">
@@ -19123,7 +19465,8 @@
         <v>0</v>
       </c>
       <c r="O344" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>45.355416001900949</v>
       </c>
     </row>
     <row r="345" spans="1:15" x14ac:dyDescent="0.35">
@@ -19170,7 +19513,8 @@
         <v>0</v>
       </c>
       <c r="O345" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>30.947958841348928</v>
       </c>
     </row>
     <row r="346" spans="1:15" x14ac:dyDescent="0.35">
@@ -19217,7 +19561,8 @@
         <v>0</v>
       </c>
       <c r="O346" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>30.356385614145051</v>
       </c>
     </row>
     <row r="347" spans="1:15" x14ac:dyDescent="0.35">
@@ -19264,7 +19609,8 @@
         <v>0</v>
       </c>
       <c r="O347" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>30.356385614145051</v>
       </c>
     </row>
     <row r="348" spans="1:15" x14ac:dyDescent="0.35">
@@ -19311,7 +19657,8 @@
         <v>0</v>
       </c>
       <c r="O348" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>50.701765449793442</v>
       </c>
     </row>
     <row r="349" spans="1:15" x14ac:dyDescent="0.35">
@@ -19358,7 +19705,8 @@
         <v>0</v>
       </c>
       <c r="O349" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>29.690865733540694</v>
       </c>
     </row>
     <row r="350" spans="1:15" x14ac:dyDescent="0.35">
@@ -19405,7 +19753,8 @@
         <v>0</v>
       </c>
       <c r="O350" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>38.597806883648538</v>
       </c>
     </row>
     <row r="351" spans="1:15" x14ac:dyDescent="0.35">
@@ -19452,7 +19801,8 @@
         <v>0</v>
       </c>
       <c r="O351" s="1">
-        <v>37.491809993363049</v>
+        <f t="shared" si="5"/>
+        <v>35.351431366515946</v>
       </c>
     </row>
     <row r="352" spans="1:15" x14ac:dyDescent="0.35">
@@ -19499,7 +19849,8 @@
         <v>0</v>
       </c>
       <c r="O352" s="1">
-        <v>36.389109699440603</v>
+        <f t="shared" si="5"/>
+        <v>35.685606940854299</v>
       </c>
     </row>
     <row r="353" spans="1:15" x14ac:dyDescent="0.35">
@@ -19546,7 +19897,8 @@
         <v>0</v>
       </c>
       <c r="O353" s="1">
-        <v>36.389109699440603</v>
+        <f t="shared" si="5"/>
+        <v>33.736671741778324</v>
       </c>
     </row>
     <row r="354" spans="1:15" x14ac:dyDescent="0.35">
@@ -19593,7 +19945,8 @@
         <v>0</v>
       </c>
       <c r="O354" s="1">
-        <v>36.389109699440603</v>
+        <f t="shared" si="5"/>
+        <v>49.210537054211272</v>
       </c>
     </row>
     <row r="355" spans="1:15" x14ac:dyDescent="0.35">
@@ -19640,7 +19993,8 @@
         <v>0</v>
       </c>
       <c r="O355" s="1">
-        <v>35.286409405518164</v>
+        <f t="shared" si="5"/>
+        <v>42.687450354730309</v>
       </c>
     </row>
     <row r="356" spans="1:15" x14ac:dyDescent="0.35">
@@ -19687,7 +20041,8 @@
         <v>0</v>
       </c>
       <c r="O356" s="1">
-        <v>35.286409405518164</v>
+        <f t="shared" si="5"/>
+        <v>42.687450354730309</v>
       </c>
     </row>
     <row r="357" spans="1:15" x14ac:dyDescent="0.35">
@@ -19707,7 +20062,7 @@
         <v>0</v>
       </c>
       <c r="F357" s="1">
-        <v>16.556760229691204</v>
+        <v>15.232219411315906</v>
       </c>
       <c r="G357" s="1">
         <v>0</v>
@@ -19734,7 +20089,8 @@
         <v>0</v>
       </c>
       <c r="O357" s="1">
-        <v>34.183709111595718</v>
+        <f t="shared" si="5"/>
+        <v>42.204883690096075</v>
       </c>
     </row>
     <row r="358" spans="1:15" x14ac:dyDescent="0.35">
@@ -19781,7 +20137,8 @@
         <v>0</v>
       </c>
       <c r="O358" s="1">
-        <v>34.183709111595718</v>
+        <f t="shared" si="5"/>
+        <v>41.807629632109261</v>
       </c>
     </row>
     <row r="359" spans="1:15" x14ac:dyDescent="0.35">
@@ -19828,7 +20185,8 @@
         <v>0</v>
       </c>
       <c r="O359" s="1">
-        <v>34.183709111595718</v>
+        <f t="shared" si="5"/>
+        <v>31.69202496954933</v>
       </c>
     </row>
     <row r="360" spans="1:15" x14ac:dyDescent="0.35">
@@ -19875,7 +20233,8 @@
         <v>0</v>
       </c>
       <c r="O360" s="1">
-        <v>33.081008817673279</v>
+        <f t="shared" si="5"/>
+        <v>40.019484707559663</v>
       </c>
     </row>
     <row r="361" spans="1:15" x14ac:dyDescent="0.35">
@@ -19907,7 +20266,7 @@
         <v>0</v>
       </c>
       <c r="J361" s="1">
-        <v>33.096377818142962</v>
+        <v>30.448667592691528</v>
       </c>
       <c r="K361" s="1">
         <v>0</v>
@@ -19922,7 +20281,8 @@
         <v>0</v>
       </c>
       <c r="O361" s="1">
-        <v>31.978308523750833</v>
+        <f t="shared" si="5"/>
+        <v>30.448667592691528</v>
       </c>
     </row>
     <row r="362" spans="1:15" x14ac:dyDescent="0.35">
@@ -19942,7 +20302,7 @@
         <v>0</v>
       </c>
       <c r="F362" s="1">
-        <v>42.144480584668514</v>
+        <v>38.772922137895037</v>
       </c>
       <c r="G362" s="1">
         <v>0</v>
@@ -19969,7 +20329,8 @@
         <v>0</v>
       </c>
       <c r="O362" s="1">
-        <v>30.875608229828391</v>
+        <f t="shared" si="5"/>
+        <v>38.772922137895037</v>
       </c>
     </row>
     <row r="363" spans="1:15" x14ac:dyDescent="0.35">
@@ -20016,7 +20377,8 @@
         <v>0</v>
       </c>
       <c r="O363" s="1">
-        <v>29.772907935905948</v>
+        <f t="shared" si="5"/>
+        <v>32.229587377445213</v>
       </c>
     </row>
     <row r="364" spans="1:15" x14ac:dyDescent="0.35">
@@ -20036,7 +20398,7 @@
         <v>0</v>
       </c>
       <c r="F364" s="1">
-        <v>40.639320563787493</v>
+        <v>37.388174918684498</v>
       </c>
       <c r="G364" s="1">
         <v>0</v>
@@ -20063,7 +20425,8 @@
         <v>0</v>
       </c>
       <c r="O364" s="1">
-        <v>29.772907935905948</v>
+        <f t="shared" si="5"/>
+        <v>37.388174918684498</v>
       </c>
     </row>
     <row r="365" spans="1:15" x14ac:dyDescent="0.35">
@@ -20110,7 +20473,8 @@
         <v>0</v>
       </c>
       <c r="O365" s="1">
-        <v>28.670207641983506</v>
+        <f t="shared" si="5"/>
+        <v>23.666086172796234</v>
       </c>
     </row>
     <row r="366" spans="1:15" x14ac:dyDescent="0.35">
@@ -20157,7 +20521,8 @@
         <v>0</v>
       </c>
       <c r="O366" s="1">
-        <v>26.464807054138621</v>
+        <f t="shared" si="5"/>
+        <v>24.535761266747869</v>
       </c>
     </row>
     <row r="367" spans="1:15" x14ac:dyDescent="0.35">
@@ -20204,7 +20569,8 @@
         <v>0</v>
       </c>
       <c r="O367" s="1">
-        <v>26.464807054138621</v>
+        <f t="shared" si="5"/>
+        <v>32.782498840346705</v>
       </c>
     </row>
     <row r="368" spans="1:15" x14ac:dyDescent="0.35">
@@ -20251,7 +20617,8 @@
         <v>0</v>
       </c>
       <c r="O368" s="1">
-        <v>26.464807054138621</v>
+        <f t="shared" si="5"/>
+        <v>19.539153567110038</v>
       </c>
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.35">
@@ -20298,7 +20665,8 @@
         <v>0</v>
       </c>
       <c r="O369" s="1">
-        <v>25.362106760216179</v>
+        <f t="shared" si="5"/>
+        <v>29.40432358080249</v>
       </c>
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.35">
@@ -20345,7 +20713,8 @@
         <v>0</v>
       </c>
       <c r="O370" s="1">
-        <v>24.259406466293733</v>
+        <f t="shared" si="5"/>
+        <v>21.907777232878047</v>
       </c>
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.35">
@@ -20392,7 +20761,8 @@
         <v>0</v>
       </c>
       <c r="O371" s="1">
-        <v>24.259406466293733</v>
+        <f t="shared" si="5"/>
+        <v>19.211736651114567</v>
       </c>
     </row>
     <row r="372" spans="1:15" x14ac:dyDescent="0.35">
@@ -20439,7 +20809,8 @@
         <v>0</v>
       </c>
       <c r="O372" s="1">
-        <v>24.259406466293733</v>
+        <f t="shared" si="5"/>
+        <v>20.025149838519894</v>
       </c>
     </row>
     <row r="373" spans="1:15" x14ac:dyDescent="0.35">
@@ -20486,7 +20857,8 @@
         <v>0</v>
       </c>
       <c r="O373" s="1">
-        <v>23.15670617237129</v>
+        <f t="shared" si="5"/>
+        <v>28.321297492719179</v>
       </c>
     </row>
     <row r="374" spans="1:15" x14ac:dyDescent="0.35">
@@ -20533,7 +20905,8 @@
         <v>0</v>
       </c>
       <c r="O374" s="1">
-        <v>23.15670617237129</v>
+        <f t="shared" si="5"/>
+        <v>28.013639295291764</v>
       </c>
     </row>
     <row r="375" spans="1:15" x14ac:dyDescent="0.35">
@@ -20553,7 +20926,7 @@
         <v>0</v>
       </c>
       <c r="F375" s="1">
-        <v>31.608360438501386</v>
+        <v>29.079691603421274</v>
       </c>
       <c r="G375" s="1">
         <v>0</v>
@@ -20580,7 +20953,8 @@
         <v>0</v>
       </c>
       <c r="O375" s="1">
-        <v>23.15670617237129</v>
+        <f t="shared" si="5"/>
+        <v>29.079691603421274</v>
       </c>
     </row>
     <row r="376" spans="1:15" x14ac:dyDescent="0.35">
@@ -20627,7 +21001,8 @@
         <v>0</v>
       </c>
       <c r="O376" s="1">
-        <v>22.054005878448848</v>
+        <f t="shared" si="5"/>
+        <v>16.282627972591698</v>
       </c>
     </row>
     <row r="377" spans="1:15" x14ac:dyDescent="0.35">
@@ -20674,7 +21049,8 @@
         <v>0</v>
       </c>
       <c r="O377" s="1">
-        <v>22.054005878448848</v>
+        <f t="shared" si="5"/>
+        <v>18.204681671381721</v>
       </c>
     </row>
     <row r="378" spans="1:15" x14ac:dyDescent="0.35">
@@ -20721,7 +21097,8 @@
         <v>0</v>
       </c>
       <c r="O378" s="1">
-        <v>22.054005878448848</v>
+        <f t="shared" si="5"/>
+        <v>18.204681671381721</v>
       </c>
     </row>
     <row r="379" spans="1:15" x14ac:dyDescent="0.35">
@@ -20768,7 +21145,8 @@
         <v>0</v>
       </c>
       <c r="O379" s="1">
-        <v>20.951305584526406</v>
+        <f t="shared" si="5"/>
+        <v>25.345673648121117</v>
       </c>
     </row>
     <row r="380" spans="1:15" x14ac:dyDescent="0.35">
@@ -20800,7 +21178,7 @@
         <v>0</v>
       </c>
       <c r="J380" s="1">
-        <v>21.683833742921252</v>
+        <v>19.94912704348755</v>
       </c>
       <c r="K380" s="1">
         <v>0</v>
@@ -20815,7 +21193,8 @@
         <v>0</v>
       </c>
       <c r="O380" s="1">
-        <v>20.951305584526406</v>
+        <f t="shared" si="5"/>
+        <v>19.94912704348755</v>
       </c>
     </row>
     <row r="381" spans="1:15" x14ac:dyDescent="0.35">
@@ -20847,7 +21226,7 @@
         <v>0</v>
       </c>
       <c r="J381" s="1">
-        <v>21.683833742921252</v>
+        <v>19.94912704348755</v>
       </c>
       <c r="K381" s="1">
         <v>0</v>
@@ -20862,7 +21241,8 @@
         <v>0</v>
       </c>
       <c r="O381" s="1">
-        <v>20.951305584526406</v>
+        <f t="shared" si="5"/>
+        <v>19.94912704348755</v>
       </c>
     </row>
     <row r="382" spans="1:15" x14ac:dyDescent="0.35">
@@ -20909,7 +21289,8 @@
         <v>0</v>
       </c>
       <c r="O382" s="1">
-        <v>20.951305584526406</v>
+        <f t="shared" si="5"/>
+        <v>20.546258541703992</v>
       </c>
     </row>
     <row r="383" spans="1:15" x14ac:dyDescent="0.35">
@@ -20956,7 +21337,8 @@
         <v>0</v>
       </c>
       <c r="O383" s="1">
-        <v>19.848605290603967</v>
+        <f t="shared" si="5"/>
+        <v>15.71869362363919</v>
       </c>
     </row>
     <row r="384" spans="1:15" x14ac:dyDescent="0.35">
@@ -21003,7 +21385,8 @@
         <v>0</v>
       </c>
       <c r="O384" s="1">
-        <v>19.848605290603967</v>
+        <f t="shared" si="5"/>
+        <v>24.011690824535798</v>
       </c>
     </row>
     <row r="385" spans="1:15" x14ac:dyDescent="0.35">
@@ -21035,7 +21418,7 @@
         <v>0</v>
       </c>
       <c r="J385" s="1">
-        <v>19.40132492787691</v>
+        <v>17.849218933646757</v>
       </c>
       <c r="K385" s="1">
         <v>0</v>
@@ -21050,7 +21433,8 @@
         <v>0</v>
       </c>
       <c r="O385" s="1">
-        <v>18.745904996681524</v>
+        <f t="shared" si="5"/>
+        <v>17.849218933646757</v>
       </c>
     </row>
     <row r="386" spans="1:15" x14ac:dyDescent="0.35">
@@ -21082,7 +21466,7 @@
         <v>0</v>
       </c>
       <c r="J386" s="1">
-        <v>19.40132492787691</v>
+        <v>17.849218933646757</v>
       </c>
       <c r="K386" s="1">
         <v>0</v>
@@ -21097,7 +21481,8 @@
         <v>0</v>
       </c>
       <c r="O386" s="1">
-        <v>18.745904996681524</v>
+        <f t="shared" si="5"/>
+        <v>17.849218933646757</v>
       </c>
     </row>
     <row r="387" spans="1:15" x14ac:dyDescent="0.35">
@@ -21144,7 +21529,8 @@
         <v>0</v>
       </c>
       <c r="O387" s="1">
-        <v>18.745904996681524</v>
+        <f t="shared" ref="O387:O432" si="6">+SUM(C387:N387)</f>
+        <v>13.840233776702943</v>
       </c>
     </row>
     <row r="388" spans="1:15" x14ac:dyDescent="0.35">
@@ -21191,7 +21577,8 @@
         <v>0</v>
       </c>
       <c r="O388" s="1">
-        <v>17.643204702759082</v>
+        <f t="shared" si="6"/>
+        <v>17.302112456171784</v>
       </c>
     </row>
     <row r="389" spans="1:15" x14ac:dyDescent="0.35">
@@ -21238,7 +21625,8 @@
         <v>0</v>
       </c>
       <c r="O389" s="1">
-        <v>17.643204702759082</v>
+        <f t="shared" si="6"/>
+        <v>19.485861378587092</v>
       </c>
     </row>
     <row r="390" spans="1:15" x14ac:dyDescent="0.35">
@@ -21285,7 +21673,8 @@
         <v>0</v>
       </c>
       <c r="O390" s="1">
-        <v>17.643204702759082</v>
+        <f t="shared" si="6"/>
+        <v>23.859654329314559</v>
       </c>
     </row>
     <row r="391" spans="1:15" x14ac:dyDescent="0.35">
@@ -21332,7 +21721,8 @@
         <v>0</v>
       </c>
       <c r="O391" s="1">
-        <v>17.643204702759082</v>
+        <f t="shared" si="6"/>
+        <v>16.357174177831912</v>
       </c>
     </row>
     <row r="392" spans="1:15" x14ac:dyDescent="0.35">
@@ -21379,7 +21769,8 @@
         <v>0</v>
       </c>
       <c r="O392" s="1">
-        <v>16.54050440883664</v>
+        <f t="shared" si="6"/>
+        <v>16.220730427661046</v>
       </c>
     </row>
     <row r="393" spans="1:15" x14ac:dyDescent="0.35">
@@ -21426,7 +21817,8 @@
         <v>0</v>
       </c>
       <c r="O393" s="1">
-        <v>16.54050440883664</v>
+        <f t="shared" si="6"/>
+        <v>20.229498209085126</v>
       </c>
     </row>
     <row r="394" spans="1:15" x14ac:dyDescent="0.35">
@@ -21473,7 +21865,8 @@
         <v>0</v>
       </c>
       <c r="O394" s="1">
-        <v>16.54050440883664</v>
+        <f t="shared" si="6"/>
+        <v>18.267995042425401</v>
       </c>
     </row>
     <row r="395" spans="1:15" x14ac:dyDescent="0.35">
@@ -21520,7 +21913,8 @@
         <v>0</v>
       </c>
       <c r="O395" s="1">
-        <v>15.437804114914195</v>
+        <f t="shared" si="6"/>
+        <v>18.880864995146119</v>
       </c>
     </row>
     <row r="396" spans="1:15" x14ac:dyDescent="0.35">
@@ -21567,7 +21961,8 @@
         <v>0</v>
       </c>
       <c r="O396" s="1">
-        <v>15.437804114914195</v>
+        <f t="shared" si="6"/>
+        <v>17.050128706263706</v>
       </c>
     </row>
     <row r="397" spans="1:15" x14ac:dyDescent="0.35">
@@ -21614,7 +22009,8 @@
         <v>0</v>
       </c>
       <c r="O397" s="1">
-        <v>15.437804114914195</v>
+        <f t="shared" si="6"/>
+        <v>14.312527405602925</v>
       </c>
     </row>
     <row r="398" spans="1:15" x14ac:dyDescent="0.35">
@@ -21661,7 +22057,8 @@
         <v>0</v>
       </c>
       <c r="O398" s="1">
-        <v>15.437804114914195</v>
+        <f t="shared" si="6"/>
+        <v>12.743277169967206</v>
       </c>
     </row>
     <row r="399" spans="1:15" x14ac:dyDescent="0.35">
@@ -21708,7 +22105,8 @@
         <v>0</v>
       </c>
       <c r="O399" s="1">
-        <v>14.335103820991753</v>
+        <f t="shared" si="6"/>
+        <v>11.833043086398117</v>
       </c>
     </row>
     <row r="400" spans="1:15" x14ac:dyDescent="0.35">
@@ -21755,7 +22153,8 @@
         <v>0</v>
       </c>
       <c r="O400" s="1">
-        <v>14.335103820991753</v>
+        <f t="shared" si="6"/>
+        <v>10.583708182184603</v>
       </c>
     </row>
     <row r="401" spans="1:15" x14ac:dyDescent="0.35">
@@ -21802,7 +22201,8 @@
         <v>0</v>
       </c>
       <c r="O401" s="1">
-        <v>14.335103820991753</v>
+        <f t="shared" si="6"/>
+        <v>15.832262370102013</v>
       </c>
     </row>
     <row r="402" spans="1:15" x14ac:dyDescent="0.35">
@@ -21849,7 +22249,8 @@
         <v>0</v>
       </c>
       <c r="O402" s="1">
-        <v>14.335103820991753</v>
+        <f t="shared" si="6"/>
+        <v>11.833043086398117</v>
       </c>
     </row>
     <row r="403" spans="1:15" x14ac:dyDescent="0.35">
@@ -21896,7 +22297,8 @@
         <v>0</v>
       </c>
       <c r="O403" s="1">
-        <v>14.335103820991753</v>
+        <f t="shared" si="6"/>
+        <v>17.341776706609185</v>
       </c>
     </row>
     <row r="404" spans="1:15" x14ac:dyDescent="0.35">
@@ -21943,7 +22345,8 @@
         <v>0</v>
       </c>
       <c r="O404" s="1">
-        <v>14.335103820991753</v>
+        <f t="shared" si="6"/>
+        <v>17.532231781207113</v>
       </c>
     </row>
     <row r="405" spans="1:15" x14ac:dyDescent="0.35">
@@ -21990,7 +22393,8 @@
         <v>0</v>
       </c>
       <c r="O405" s="1">
-        <v>13.232403527069311</v>
+        <f t="shared" si="6"/>
+        <v>12.267880633373935</v>
       </c>
     </row>
     <row r="406" spans="1:15" x14ac:dyDescent="0.35">
@@ -22037,7 +22441,8 @@
         <v>0</v>
       </c>
       <c r="O406" s="1">
-        <v>13.232403527069311</v>
+        <f t="shared" si="6"/>
+        <v>16.183598567268103</v>
       </c>
     </row>
     <row r="407" spans="1:15" x14ac:dyDescent="0.35">
@@ -22084,7 +22489,8 @@
         <v>0</v>
       </c>
       <c r="O407" s="1">
-        <v>13.232403527069311</v>
+        <f t="shared" si="6"/>
+        <v>14.614396033940318</v>
       </c>
     </row>
     <row r="408" spans="1:15" x14ac:dyDescent="0.35">
@@ -22131,7 +22537,8 @@
         <v>0</v>
       </c>
       <c r="O408" s="1">
-        <v>13.232403527069311</v>
+        <f t="shared" si="6"/>
+        <v>14.614396033940318</v>
       </c>
     </row>
     <row r="409" spans="1:15" x14ac:dyDescent="0.35">
@@ -22178,7 +22585,8 @@
         <v>0</v>
       </c>
       <c r="O409" s="1">
-        <v>13.232403527069311</v>
+        <f t="shared" si="6"/>
+        <v>12.976584342128838</v>
       </c>
     </row>
     <row r="410" spans="1:15" x14ac:dyDescent="0.35">
@@ -22198,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="F410" s="1">
-        <v>16.556760229691204</v>
+        <v>15.232219411315906</v>
       </c>
       <c r="G410" s="1">
         <v>0</v>
@@ -22225,7 +22633,8 @@
         <v>0</v>
       </c>
       <c r="O410" s="1">
-        <v>12.129703233146866</v>
+        <f t="shared" si="6"/>
+        <v>15.232219411315906</v>
       </c>
     </row>
     <row r="411" spans="1:15" x14ac:dyDescent="0.35">
@@ -22245,7 +22654,7 @@
         <v>0</v>
       </c>
       <c r="F411" s="1">
-        <v>16.556760229691204</v>
+        <v>15.232219411315906</v>
       </c>
       <c r="G411" s="1">
         <v>0</v>
@@ -22272,7 +22681,8 @@
         <v>0</v>
       </c>
       <c r="O411" s="1">
-        <v>12.129703233146866</v>
+        <f t="shared" si="6"/>
+        <v>15.232219411315906</v>
       </c>
     </row>
     <row r="412" spans="1:15" x14ac:dyDescent="0.35">
@@ -22319,7 +22729,8 @@
         <v>0</v>
       </c>
       <c r="O412" s="1">
-        <v>12.129703233146866</v>
+        <f t="shared" si="6"/>
+        <v>11.245557247259441</v>
       </c>
     </row>
     <row r="413" spans="1:15" x14ac:dyDescent="0.35">
@@ -22339,7 +22750,7 @@
         <v>0</v>
       </c>
       <c r="F413" s="1">
-        <v>16.556760229691204</v>
+        <v>15.232219411315906</v>
       </c>
       <c r="G413" s="1">
         <v>0</v>
@@ -22366,7 +22777,8 @@
         <v>0</v>
       </c>
       <c r="O413" s="1">
-        <v>12.129703233146866</v>
+        <f t="shared" si="6"/>
+        <v>15.232219411315906</v>
       </c>
     </row>
     <row r="414" spans="1:15" x14ac:dyDescent="0.35">
@@ -22413,7 +22825,8 @@
         <v>0</v>
       </c>
       <c r="O414" s="1">
-        <v>12.129703233146866</v>
+        <f t="shared" si="6"/>
+        <v>14.834965353329094</v>
       </c>
     </row>
     <row r="415" spans="1:15" x14ac:dyDescent="0.35">
@@ -22460,7 +22873,8 @@
         <v>0</v>
       </c>
       <c r="O415" s="1">
-        <v>11.027002939224424</v>
+        <f t="shared" si="6"/>
+        <v>12.178663361616932</v>
       </c>
     </row>
     <row r="416" spans="1:15" x14ac:dyDescent="0.35">
@@ -22492,7 +22906,7 @@
         <v>0</v>
       </c>
       <c r="J416" s="1">
-        <v>11.412544075221712</v>
+        <v>10.499540549203974</v>
       </c>
       <c r="K416" s="1">
         <v>0</v>
@@ -22507,7 +22921,8 @@
         <v>0</v>
       </c>
       <c r="O416" s="1">
-        <v>11.027002939224424</v>
+        <f t="shared" si="6"/>
+        <v>10.499540549203974</v>
       </c>
     </row>
     <row r="417" spans="1:15" x14ac:dyDescent="0.35">
@@ -22554,7 +22969,8 @@
         <v>0</v>
       </c>
       <c r="O417" s="1">
-        <v>11.027002939224424</v>
+        <f t="shared" si="6"/>
+        <v>13.33982823585322</v>
       </c>
     </row>
     <row r="418" spans="1:15" x14ac:dyDescent="0.35">
@@ -22601,7 +23017,8 @@
         <v>0</v>
       </c>
       <c r="O418" s="1">
-        <v>11.027002939224424</v>
+        <f t="shared" si="6"/>
+        <v>13.33982823585322</v>
       </c>
     </row>
     <row r="419" spans="1:15" x14ac:dyDescent="0.35">
@@ -22648,7 +23065,8 @@
         <v>0</v>
       </c>
       <c r="O419" s="1">
-        <v>11.027002939224424</v>
+        <f t="shared" si="6"/>
+        <v>8.7326075686884383</v>
       </c>
     </row>
     <row r="420" spans="1:15" x14ac:dyDescent="0.35">
@@ -22668,7 +23086,7 @@
         <v>0</v>
       </c>
       <c r="F420" s="1">
-        <v>13.546440187929166</v>
+        <v>12.462724972894833</v>
       </c>
       <c r="G420" s="1">
         <v>0</v>
@@ -22695,7 +23113,8 @@
         <v>0</v>
       </c>
       <c r="O420" s="1">
-        <v>9.9243026453019834</v>
+        <f t="shared" si="6"/>
+        <v>12.462724972894833</v>
       </c>
     </row>
     <row r="421" spans="1:15" x14ac:dyDescent="0.35">
@@ -22715,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="F421" s="1">
-        <v>13.546440187929166</v>
+        <v>12.462724972894833</v>
       </c>
       <c r="G421" s="1">
         <v>0</v>
@@ -22742,7 +23161,8 @@
         <v>0</v>
       </c>
       <c r="O421" s="1">
-        <v>9.9243026453019834</v>
+        <f t="shared" si="6"/>
+        <v>12.462724972894833</v>
       </c>
     </row>
     <row r="422" spans="1:15" x14ac:dyDescent="0.35">
@@ -22789,7 +23209,8 @@
         <v>0</v>
       </c>
       <c r="O422" s="1">
-        <v>8.821602351379541</v>
+        <f t="shared" si="6"/>
+        <v>11.929827164657279</v>
       </c>
     </row>
     <row r="423" spans="1:15" x14ac:dyDescent="0.35">
@@ -22836,7 +23257,8 @@
         <v>0</v>
       </c>
       <c r="O423" s="1">
-        <v>8.821602351379541</v>
+        <f t="shared" si="6"/>
+        <v>8.1785870889159558</v>
       </c>
     </row>
     <row r="424" spans="1:15" x14ac:dyDescent="0.35">
@@ -22883,7 +23305,8 @@
         <v>0</v>
       </c>
       <c r="O424" s="1">
-        <v>8.821602351379541</v>
+        <f t="shared" si="6"/>
+        <v>8.651056228085892</v>
       </c>
     </row>
     <row r="425" spans="1:15" x14ac:dyDescent="0.35">
@@ -22930,7 +23353,8 @@
         <v>0</v>
       </c>
       <c r="O425" s="1">
-        <v>8.821602351379541</v>
+        <f t="shared" si="6"/>
+        <v>8.651056228085892</v>
       </c>
     </row>
     <row r="426" spans="1:15" x14ac:dyDescent="0.35">
@@ -22977,7 +23401,8 @@
         <v>0</v>
       </c>
       <c r="O426" s="1">
-        <v>7.7189020574570977</v>
+        <f t="shared" si="6"/>
+        <v>9.4404324975730596</v>
       </c>
     </row>
     <row r="427" spans="1:15" x14ac:dyDescent="0.35">
@@ -23024,7 +23449,8 @@
         <v>0</v>
       </c>
       <c r="O427" s="1">
-        <v>7.7189020574570977</v>
+        <f t="shared" si="6"/>
+        <v>9.4404324975730596</v>
       </c>
     </row>
     <row r="428" spans="1:15" x14ac:dyDescent="0.35">
@@ -23071,7 +23497,8 @@
         <v>0</v>
       </c>
       <c r="O428" s="1">
-        <v>7.7189020574570977</v>
+        <f t="shared" si="6"/>
+        <v>8.5250643531318531</v>
       </c>
     </row>
     <row r="429" spans="1:15" x14ac:dyDescent="0.35">
@@ -23118,7 +23545,8 @@
         <v>0</v>
       </c>
       <c r="O429" s="1">
-        <v>6.6162017635346553</v>
+        <f t="shared" si="6"/>
+        <v>5.2395645412130643</v>
       </c>
     </row>
     <row r="430" spans="1:15" x14ac:dyDescent="0.35">
@@ -23165,7 +23593,8 @@
         <v>0</v>
       </c>
       <c r="O430" s="1">
-        <v>5.513501469612212</v>
+        <f t="shared" si="6"/>
+        <v>4.3663037843442192</v>
       </c>
     </row>
     <row r="431" spans="1:15" x14ac:dyDescent="0.35">
@@ -23212,7 +23641,8 @@
         <v>0</v>
       </c>
       <c r="O431" s="1">
-        <v>5.513501469612212</v>
+        <f t="shared" si="6"/>
+        <v>4.3663037843442192</v>
       </c>
     </row>
     <row r="432" spans="1:15" x14ac:dyDescent="0.35">
@@ -23259,7 +23689,8 @@
         <v>0</v>
       </c>
       <c r="O432" s="1">
-        <v>-109.1673290983218</v>
+        <f t="shared" si="6"/>
+        <v>-76.114647551230064</v>
       </c>
     </row>
   </sheetData>
